--- a/data/Master Standardisation DACCS_LE.xlsx
+++ b/data/Master Standardisation DACCS_LE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28803"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/ksievert_ethz_ch/Documents/SAF/_DACCS vs Synfuels/Meta Analysis_DACCS/4 Harmonization/Harmonization Sheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/ydubey_ethz_ch/Documents/Documents/GitHub/DACCSvDACCU/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6766" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8995197C-C705-47D3-A39C-A2D6721E81DA}"/>
+  <xr:revisionPtr revIDLastSave="6797" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B405949-A78B-4C0D-BDCA-D62C47D81B89}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="973" firstSheet="2" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="973" firstSheet="6" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -60,9 +60,9 @@
     <externalReference r:id="rId43"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Standardization Results'!$A$2:$W$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Studies current &amp;future cost'!$A$1:$AL$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Study Parameters'!$A$1:$AL$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Standardization Results'!$A$2:$W$180</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -3374,17 +3374,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="170" formatCode="_ * #,##0.00000_ ;_ * \-#,##0.00000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="171" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="172" formatCode="0.0000"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="169" formatCode="_ * #,##0.00000_ ;_ * \-#,##0.00000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="171" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3908,7 +3908,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3929,21 +3929,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -3984,8 +3984,8 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4046,10 +4046,10 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4064,7 +4064,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
@@ -4073,16 +4073,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="35" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="35" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -4118,7 +4118,7 @@
     <xf numFmtId="0" fontId="32" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="10" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4582,13 +4582,13 @@
             <v>255.52576857651488</v>
           </cell>
           <cell r="G31">
-            <v>78.932509034299216</v>
+            <v>84.85212367835156</v>
           </cell>
           <cell r="I31">
             <v>255.52576857651488</v>
           </cell>
           <cell r="L31">
-            <v>61.275246906565449</v>
+            <v>67.202982248777587</v>
           </cell>
         </row>
       </sheetData>
@@ -4598,13 +4598,13 @@
             <v>255.52576857651488</v>
           </cell>
           <cell r="G31">
-            <v>78.932509034299216</v>
+            <v>84.85212367835156</v>
           </cell>
           <cell r="I31">
             <v>255.52576857651488</v>
           </cell>
           <cell r="L31">
-            <v>61.275246906565449</v>
+            <v>67.202982248777587</v>
           </cell>
         </row>
       </sheetData>
@@ -4613,14 +4613,8 @@
           <cell r="D34">
             <v>292.47958561757542</v>
           </cell>
-          <cell r="G34">
-            <v>102.02864468496207</v>
-          </cell>
           <cell r="I34">
             <v>292.47958561757542</v>
-          </cell>
-          <cell r="L34">
-            <v>84.371382557228301</v>
           </cell>
         </row>
       </sheetData>
@@ -4647,13 +4641,13 @@
             <v>252.26048677321859</v>
           </cell>
           <cell r="G31">
-            <v>51.583582450093708</v>
+            <v>95.725439543447692</v>
           </cell>
           <cell r="I31">
             <v>252.26048677321859</v>
           </cell>
           <cell r="L31">
-            <v>31.069148068405784</v>
+            <v>75.211005161759758</v>
           </cell>
         </row>
       </sheetData>
@@ -4663,13 +4657,13 @@
             <v>252.26048677321859</v>
           </cell>
           <cell r="G31">
-            <v>51.583582450093708</v>
+            <v>95.725439543447692</v>
           </cell>
           <cell r="I31">
             <v>252.26048677321859</v>
           </cell>
           <cell r="L31">
-            <v>31.069148068405784</v>
+            <v>75.211005161759758</v>
           </cell>
         </row>
       </sheetData>
@@ -4678,14 +4672,8 @@
           <cell r="D34">
             <v>289.21430381427916</v>
           </cell>
-          <cell r="G34">
-            <v>74.67971810075656</v>
-          </cell>
           <cell r="I34">
             <v>289.21430381427916</v>
-          </cell>
-          <cell r="L34">
-            <v>54.16528371906864</v>
           </cell>
         </row>
       </sheetData>
@@ -5118,17 +5106,7 @@
       <sheetData sheetId="2">
         <row r="15">
           <cell r="I15">
-            <v>161.70897790330613</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="I16">
-            <v>104.86798641060018</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="I17">
-            <v>300.09200804319312</v>
+            <v>170.41354109154099</v>
           </cell>
         </row>
       </sheetData>
@@ -5631,7 +5609,7 @@
             <v>145.45192472670769</v>
           </cell>
           <cell r="F24">
-            <v>110.40334766355258</v>
+            <v>112.66928210128302</v>
           </cell>
         </row>
       </sheetData>
@@ -5647,7 +5625,7 @@
             <v>154.3621577744924</v>
           </cell>
           <cell r="F24">
-            <v>118.09146086248863</v>
+            <v>120.35739530021907</v>
           </cell>
         </row>
       </sheetData>
@@ -5661,9 +5639,6 @@
           </cell>
           <cell r="E27">
             <v>194.3621577744924</v>
-          </cell>
-          <cell r="F27">
-            <v>143.09146086248865</v>
           </cell>
         </row>
       </sheetData>
@@ -5696,7 +5671,7 @@
             <v>186.68727529198395</v>
           </cell>
           <cell r="F24">
-            <v>145.98289325383018</v>
+            <v>148.24882769156065</v>
           </cell>
         </row>
       </sheetData>
@@ -5712,7 +5687,7 @@
             <v>154.3621577744924</v>
           </cell>
           <cell r="F24">
-            <v>118.09146086248863</v>
+            <v>120.35739530021907</v>
           </cell>
         </row>
       </sheetData>
@@ -5726,9 +5701,6 @@
           </cell>
           <cell r="E27">
             <v>194.3621577744924</v>
-          </cell>
-          <cell r="F27">
-            <v>143.09146086248865</v>
           </cell>
         </row>
       </sheetData>
@@ -6007,7 +5979,7 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>118.45853215160149</v>
+            <v>134.11219617439485</v>
           </cell>
         </row>
       </sheetData>
@@ -6019,7 +5991,7 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>106.84340810280642</v>
+            <v>122.49707212559984</v>
           </cell>
         </row>
       </sheetData>
@@ -6027,11 +5999,6 @@
         <row r="11">
           <cell r="B11">
             <v>295.30442580438057</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21">
-            <v>131.84340810280642</v>
           </cell>
         </row>
       </sheetData>
@@ -6076,7 +6043,7 @@
             <v>223.41019772115243</v>
           </cell>
           <cell r="G23">
-            <v>136.97848574432413</v>
+            <v>139.37212947003994</v>
           </cell>
         </row>
       </sheetData>
@@ -6092,7 +6059,7 @@
             <v>223.41019772115243</v>
           </cell>
           <cell r="G23">
-            <v>136.97848574432413</v>
+            <v>139.37212947003994</v>
           </cell>
         </row>
       </sheetData>
@@ -6106,9 +6073,6 @@
           </cell>
           <cell r="E23">
             <v>263.41019772115243</v>
-          </cell>
-          <cell r="G23">
-            <v>161.3365262382693</v>
           </cell>
         </row>
       </sheetData>
@@ -6348,17 +6312,7 @@
       <sheetData sheetId="2">
         <row r="15">
           <cell r="I15">
-            <v>204.09122311913183</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="I16">
-            <v>107.86441779994588</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="I17">
-            <v>471.65350886798007</v>
+            <v>233.35148149487728</v>
           </cell>
         </row>
       </sheetData>
@@ -6496,17 +6450,7 @@
       <sheetData sheetId="2">
         <row r="2">
           <cell r="I2">
-            <v>906.63214812469676</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="I3">
-            <v>795.12799940002435</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1096.6745626767736</v>
+            <v>1173.97198503103</v>
           </cell>
         </row>
       </sheetData>
@@ -6644,17 +6588,7 @@
       <sheetData sheetId="2">
         <row r="2">
           <cell r="I2">
-            <v>367.37217040690308</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="I3">
-            <v>275.02033803264993</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>524.6187562771147</v>
+            <v>416.10639561160389</v>
           </cell>
         </row>
       </sheetData>
@@ -7404,9 +7338,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8418090-0B0B-C248-B9C6-3EA8C5996CC0}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7420,33 +7354,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E9E050F-07F8-FE48-85C0-51954A76FC24}">
   <sheetPr codeName="Sheet6" filterMode="1"/>
   <dimension ref="A1:AL47"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.125" customWidth="1"/>
-    <col min="2" max="2" width="9.125" customWidth="1"/>
+    <col min="1" max="1" width="23.09765625" customWidth="1"/>
+    <col min="2" max="2" width="9.09765625" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="18.5" customWidth="1"/>
-    <col min="7" max="7" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.59765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.875" customWidth="1"/>
-    <col min="12" max="12" width="26.75" customWidth="1"/>
+    <col min="11" max="11" width="6.8984375" customWidth="1"/>
+    <col min="12" max="12" width="26.69921875" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="18.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.125" customWidth="1"/>
-    <col min="19" max="22" width="20.125" customWidth="1"/>
+    <col min="18" max="18" width="18.09765625" customWidth="1"/>
+    <col min="19" max="22" width="20.09765625" customWidth="1"/>
     <col min="24" max="25" width="17.5" customWidth="1"/>
-    <col min="26" max="28" width="15.125" customWidth="1"/>
+    <col min="26" max="28" width="15.09765625" customWidth="1"/>
     <col min="29" max="29" width="22.5" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="22.5" customWidth="1"/>
-    <col min="32" max="32" width="37.625" customWidth="1"/>
+    <col min="32" max="32" width="37.59765625" customWidth="1"/>
     <col min="33" max="33" width="19" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="19" customWidth="1"/>
-    <col min="36" max="36" width="33.625" customWidth="1"/>
+    <col min="36" max="36" width="33.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="51" customFormat="1">
+    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -7560,7 +7494,7 @@
       </c>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -7667,7 +7601,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:38">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -7767,7 +7701,7 @@
       </c>
       <c r="AI3" s="53"/>
     </row>
-    <row r="4" spans="1:38">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -7867,7 +7801,7 @@
       </c>
       <c r="AI4" s="53"/>
     </row>
-    <row r="5" spans="1:38">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -7967,7 +7901,7 @@
       </c>
       <c r="AI5" s="53"/>
     </row>
-    <row r="6" spans="1:38">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>185</v>
       </c>
@@ -8066,7 +8000,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="7" spans="1:38">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>185</v>
       </c>
@@ -8165,7 +8099,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:38">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>185</v>
       </c>
@@ -8264,7 +8198,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:38" hidden="1">
+    <row r="9" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>199</v>
       </c>
@@ -8363,7 +8297,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="10" spans="1:38" hidden="1">
+    <row r="10" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>208</v>
       </c>
@@ -8467,7 +8401,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="11" spans="1:38">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>214</v>
       </c>
@@ -8556,7 +8490,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:38">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>214</v>
       </c>
@@ -8640,7 +8574,7 @@
       </c>
       <c r="AI12" s="53"/>
     </row>
-    <row r="13" spans="1:38" hidden="1">
+    <row r="13" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>223</v>
       </c>
@@ -8731,7 +8665,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:38" hidden="1">
+    <row r="14" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>227</v>
       </c>
@@ -8825,7 +8759,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="15" spans="1:38" hidden="1">
+    <row r="15" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>230</v>
       </c>
@@ -8921,7 +8855,7 @@
       </c>
       <c r="AL15" s="48"/>
     </row>
-    <row r="16" spans="1:38" hidden="1">
+    <row r="16" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>230</v>
       </c>
@@ -9017,7 +8951,7 @@
       </c>
       <c r="AL16" s="48"/>
     </row>
-    <row r="17" spans="1:37" hidden="1">
+    <row r="17" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>234</v>
       </c>
@@ -9109,7 +9043,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="18" spans="1:37" s="58" customFormat="1" hidden="1">
+    <row r="18" spans="1:37" s="58" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="58" t="s">
         <v>240</v>
       </c>
@@ -9204,7 +9138,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="19" spans="1:37" hidden="1">
+    <row r="19" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>247</v>
       </c>
@@ -9291,7 +9225,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="20" spans="1:37" hidden="1">
+    <row r="20" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>247</v>
       </c>
@@ -9378,7 +9312,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="21" spans="1:37" s="48" customFormat="1" hidden="1">
+    <row r="21" spans="1:37" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="48" t="s">
         <v>251</v>
       </c>
@@ -9402,7 +9336,7 @@
       </c>
       <c r="AH21"/>
     </row>
-    <row r="22" spans="1:37" hidden="1">
+    <row r="22" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>255</v>
       </c>
@@ -9501,7 +9435,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="23" spans="1:37" hidden="1">
+    <row r="23" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>267</v>
       </c>
@@ -9605,7 +9539,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="24" spans="1:37" hidden="1">
+    <row r="24" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>267</v>
       </c>
@@ -9709,7 +9643,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="25" spans="1:37" s="60" customFormat="1" hidden="1">
+    <row r="25" spans="1:37" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="60" t="s">
         <v>271</v>
       </c>
@@ -9738,7 +9672,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="26" spans="1:37">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>275</v>
       </c>
@@ -9827,7 +9761,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="27" spans="1:37" hidden="1">
+    <row r="27" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>278</v>
       </c>
@@ -9928,7 +9862,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="28" spans="1:37" hidden="1">
+    <row r="28" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="88" t="s">
         <v>285</v>
       </c>
@@ -10004,7 +9938,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="29" spans="1:37" hidden="1">
+    <row r="29" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="88" t="s">
         <v>285</v>
       </c>
@@ -10080,7 +10014,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="30" spans="1:37" hidden="1">
+    <row r="30" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="88" t="s">
         <v>285</v>
       </c>
@@ -10156,7 +10090,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="25.9" hidden="1" customHeight="1">
+    <row r="31" spans="1:37" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="88" t="s">
         <v>285</v>
       </c>
@@ -10232,7 +10166,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="32" spans="1:37" s="48" customFormat="1" hidden="1">
+    <row r="32" spans="1:37" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="48" t="s">
         <v>290</v>
       </c>
@@ -10256,7 +10190,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="33" spans="1:37" s="58" customFormat="1" hidden="1">
+    <row r="33" spans="1:37" s="58" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="58" t="s">
         <v>294</v>
       </c>
@@ -10345,7 +10279,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="34" spans="1:37" hidden="1">
+    <row r="34" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>301</v>
       </c>
@@ -10431,7 +10365,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="35" spans="1:37" hidden="1">
+    <row r="35" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>307</v>
       </c>
@@ -10523,7 +10457,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="36" spans="1:37" hidden="1">
+    <row r="36" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>311</v>
       </c>
@@ -10615,7 +10549,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="37" spans="1:37" hidden="1">
+    <row r="37" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>315</v>
       </c>
@@ -10707,7 +10641,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="38" spans="1:37" hidden="1">
+    <row r="38" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="48" t="s">
         <v>319</v>
       </c>
@@ -10721,7 +10655,7 @@
       </c>
       <c r="F38" s="48"/>
     </row>
-    <row r="39" spans="1:37">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>329</v>
       </c>
@@ -10818,7 +10752,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="40" spans="1:37">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>329</v>
       </c>
@@ -10914,7 +10848,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="41" spans="1:37" hidden="1">
+    <row r="41" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="55" t="s">
         <v>336</v>
       </c>
@@ -11006,7 +10940,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="42" spans="1:37" hidden="1">
+    <row r="42" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="55" t="s">
         <v>342</v>
       </c>
@@ -11089,7 +11023,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="43" spans="1:37" s="92" customFormat="1" hidden="1">
+    <row r="43" spans="1:37" s="92" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="55" t="s">
         <v>345</v>
       </c>
@@ -11177,7 +11111,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="44" spans="1:37" s="92" customFormat="1" hidden="1">
+    <row r="44" spans="1:37" s="92" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="55" t="s">
         <v>345</v>
       </c>
@@ -11262,7 +11196,7 @@
       </c>
       <c r="AH44"/>
     </row>
-    <row r="45" spans="1:37" hidden="1">
+    <row r="45" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>348</v>
       </c>
@@ -11340,10 +11274,10 @@
         <v>450</v>
       </c>
     </row>
-    <row r="46" spans="1:37" hidden="1">
+    <row r="46" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="48"/>
     </row>
-    <row r="47" spans="1:37" hidden="1"/>
+    <row r="47" spans="1:37" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A1:AL47" xr:uid="{2E9E050F-07F8-FE48-85C0-51954A76FC24}">
     <filterColumn colId="0">
@@ -11389,25 +11323,25 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:W180"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="40.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.625" customWidth="1"/>
-    <col min="6" max="6" width="8.875" customWidth="1"/>
-    <col min="7" max="7" width="19.625" customWidth="1"/>
+    <col min="4" max="4" width="40.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.59765625" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" customWidth="1"/>
+    <col min="7" max="7" width="19.59765625" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="15.375" customWidth="1"/>
-    <col min="11" max="11" width="13.625" customWidth="1"/>
-    <col min="12" max="13" width="24.125" customWidth="1"/>
-    <col min="14" max="14" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="22" width="18.125" customWidth="1"/>
+    <col min="10" max="10" width="15.3984375" customWidth="1"/>
+    <col min="11" max="11" width="13.59765625" customWidth="1"/>
+    <col min="12" max="13" width="24.09765625" customWidth="1"/>
+    <col min="14" max="14" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="22" width="18.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="L1" s="144" t="s">
         <v>655</v>
       </c>
@@ -11422,7 +11356,7 @@
       <c r="Q1" s="144"/>
       <c r="R1" s="144"/>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -11493,7 +11427,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="3" spans="1:23" hidden="1">
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -11539,7 +11473,7 @@
         <v>414.8542592918007</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -11584,7 +11518,7 @@
         <v>342.50358359189738</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -11629,7 +11563,7 @@
         <v>523.95174204407829</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>151</v>
       </c>
@@ -11669,11 +11603,10 @@
       </c>
       <c r="M6" s="30"/>
       <c r="O6" s="30">
-        <f>'[2]Inputs and TEA calculations'!$I$15* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>178.17125904435753</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -11713,11 +11646,10 @@
       </c>
       <c r="M7" s="30"/>
       <c r="O7" s="30">
-        <f>'[2]Inputs and TEA calculations'!$I$16* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>115.54374663969233</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>151</v>
       </c>
@@ -11757,11 +11689,10 @@
       </c>
       <c r="M8" s="30"/>
       <c r="O8" s="30">
-        <f>'[2]Inputs and TEA calculations'!$I$17* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>330.64194453183813</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" hidden="1">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>'Study Parameters'!A3</f>
         <v>Young et al. 2023</v>
@@ -11812,7 +11743,7 @@
         <v>2060.169523488109</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1">
+    <row r="10" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -11857,7 +11788,7 @@
         <v>1488.7216799143798</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1">
+    <row r="11" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>151</v>
       </c>
@@ -11902,7 +11833,7 @@
         <v>2729.5646158724885</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>151</v>
       </c>
@@ -11943,11 +11874,10 @@
       <c r="M12" s="30"/>
       <c r="N12" s="30"/>
       <c r="O12" s="30">
-        <f>'[4]Inputs and TEA calculations'!$I$15* ((1+Inputs!$C$5) ^ (2023-G12))</f>
-        <v>224.86809733459555</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>151</v>
       </c>
@@ -11988,11 +11918,10 @@
       <c r="M13" s="30"/>
       <c r="N13" s="30"/>
       <c r="O13" s="30">
-        <f>'[4]Inputs and TEA calculations'!$I$16* ((1+Inputs!$C$5) ^ (2023-G13))</f>
-        <v>118.84522043664496</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>151</v>
       </c>
@@ -12033,11 +11962,10 @@
       <c r="M14" s="30"/>
       <c r="N14" s="30"/>
       <c r="O14" s="30">
-        <f>'[4]Inputs and TEA calculations'!$I$17* ((1+Inputs!$C$5) ^ (2023-G14))</f>
-        <v>519.66873204743047</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" hidden="1">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>'Study Parameters'!A4</f>
         <v>Young et al. 2023</v>
@@ -12087,7 +12015,7 @@
         <v>1308.9151041939408</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1">
+    <row r="16" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>151</v>
       </c>
@@ -12131,7 +12059,7 @@
         <v>1185.9075603382862</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1">
+    <row r="17" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>151</v>
       </c>
@@ -12175,7 +12103,7 @@
         <v>1518.5576325147504</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>151</v>
       </c>
@@ -12215,11 +12143,10 @@
       </c>
       <c r="M18" s="30"/>
       <c r="O18" s="139">
-        <f>'[6]Inputs and TEA calculations'!$I$2* ((1+Inputs!$C$5) ^ (2023-G18))</f>
-        <v>998.92902308774705</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>151</v>
       </c>
@@ -12259,11 +12186,10 @@
       </c>
       <c r="M19" s="30"/>
       <c r="O19" s="139">
-        <f>'[6]Inputs and TEA calculations'!$I$3* ((1+Inputs!$C$5) ^ (2023-G19))</f>
-        <v>876.07354020402272</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -12303,11 +12229,10 @@
       </c>
       <c r="M20" s="30"/>
       <c r="O20" s="139">
-        <f>'[6]Inputs and TEA calculations'!$I$4* ((1+Inputs!$C$5) ^ (2023-G20))</f>
-        <v>1208.3181164553391</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" hidden="1">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>'Study Parameters'!A5</f>
         <v>Young et al. 2023</v>
@@ -12357,7 +12282,7 @@
         <v>484.59306078439545</v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1">
+    <row r="22" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>151</v>
       </c>
@@ -12401,7 +12326,7 @@
         <v>382.81191676230259</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1">
+    <row r="23" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>151</v>
       </c>
@@ -12445,7 +12370,7 @@
         <v>657.89384726964306</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>151</v>
       </c>
@@ -12485,11 +12410,10 @@
       </c>
       <c r="M24" s="30"/>
       <c r="O24" s="139">
-        <f>'[8]Inputs and TEA calculations'!$I$2* ((1+Inputs!$C$5) ^ (2023-G24))</f>
-        <v>404.77135523294874</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>151</v>
       </c>
@@ -12529,11 +12453,10 @@
       </c>
       <c r="M25" s="30"/>
       <c r="O25" s="139">
-        <f>'[8]Inputs and TEA calculations'!$I$3* ((1+Inputs!$C$5) ^ (2023-G25))</f>
-        <v>303.01793088681831</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>151</v>
       </c>
@@ -12573,11 +12496,10 @@
       </c>
       <c r="M26" s="30"/>
       <c r="O26" s="139">
-        <f>'[8]Inputs and TEA calculations'!$I$4* ((1+Inputs!$C$5) ^ (2023-G26))</f>
-        <v>578.02594225825874</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" hidden="1">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="48" t="str">
         <f>'Study Parameters'!A6</f>
         <v>Sievert et al. 2024</v>
@@ -12626,7 +12548,7 @@
         <v>669.94069463308699</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1">
+    <row r="28" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>185</v>
       </c>
@@ -12670,7 +12592,7 @@
         <v>521.31303134173265</v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1">
+    <row r="29" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>185</v>
       </c>
@@ -12714,7 +12636,7 @@
         <v>894.39776183919753</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>185</v>
       </c>
@@ -12754,11 +12676,10 @@
       </c>
       <c r="M30" s="30"/>
       <c r="O30" s="30">
-        <f>[9]LS_summary!$J$51</f>
         <v>349</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>185</v>
       </c>
@@ -12798,11 +12719,10 @@
       </c>
       <c r="M31" s="30"/>
       <c r="O31" s="30">
-        <f>[9]LS_summary!$R$51</f>
         <v>226</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>185</v>
       </c>
@@ -12842,11 +12762,10 @@
       </c>
       <c r="M32" s="30"/>
       <c r="O32" s="30">
-        <f>[9]LS_summary!$B$51</f>
         <v>532</v>
       </c>
     </row>
-    <row r="33" spans="1:15" hidden="1">
+    <row r="33" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>'Study Parameters'!A7</f>
         <v>Sievert et al. 2024</v>
@@ -12895,7 +12814,7 @@
         <v>1282.314450530346</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1">
+    <row r="34" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>185</v>
       </c>
@@ -12938,7 +12857,7 @@
         <v>1180.094323057237</v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1">
+    <row r="35" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>185</v>
       </c>
@@ -12981,7 +12900,7 @@
         <v>1392.3242644152151</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -13021,11 +12940,10 @@
       </c>
       <c r="M36" s="30"/>
       <c r="O36" s="30">
-        <f>[9]SS_summary!$J$51</f>
         <v>441</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>185</v>
       </c>
@@ -13065,11 +12983,10 @@
       </c>
       <c r="M37" s="30"/>
       <c r="O37" s="30">
-        <f>'[9]SS_summary_11$MWh'!$R$51</f>
         <v>280</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>185</v>
       </c>
@@ -13113,7 +13030,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <f>'Study Parameters'!A8</f>
         <v>Sievert et al. 2024</v>
@@ -13162,7 +13079,7 @@
         <v>2481.3480043001368</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>185</v>
       </c>
@@ -13205,7 +13122,7 @@
         <v>2153.1601565847341</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>185</v>
       </c>
@@ -13248,7 +13165,7 @@
         <v>2874.3199941446942</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>185</v>
       </c>
@@ -13292,7 +13209,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>185</v>
       </c>
@@ -13336,7 +13253,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>185</v>
       </c>
@@ -13380,7 +13297,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13433,7 +13350,7 @@
         <v>293.01246179996224</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13488,7 +13405,7 @@
         <v>267.3339028754757</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13543,7 +13460,7 @@
         <v>303.19697040786667</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13590,7 +13507,7 @@
         <v>278.51244114406211</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13637,7 +13554,7 @@
         <v>260.17305813012763</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13684,7 +13601,7 @@
         <v>334.02175471233329</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13731,7 +13648,7 @@
         <v>347.52430793993972</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13778,7 +13695,7 @@
         <v>431.20952014305874</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13825,7 +13742,7 @@
         <v>405.58125796275607</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13872,7 +13789,7 @@
         <v>532.88151930075014</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13923,7 +13840,7 @@
         <v>598.00725415939087</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13969,7 +13886,7 @@
         <v>594.26871158968584</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -14015,7 +13932,7 @@
         <v>556.61504560775791</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -14061,7 +13978,7 @@
         <v>745.92213758183834</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -14107,7 +14024,7 @@
         <v>863.3220713069054</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
         <f>'Study Parameters'!A11</f>
         <v>Fasihi et al. 2019</v>
@@ -14164,7 +14081,7 @@
         <v>289.21430381427916</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>214</v>
       </c>
@@ -14215,7 +14132,7 @@
         <v>289.21430381427916</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>214</v>
       </c>
@@ -14255,18 +14172,17 @@
       </c>
       <c r="M62" s="30">
         <f>'[12]Step 1 LCOE LS'!$L$31* ((1+Inputs!$C$5) ^ (2022-G62))</f>
-        <v>34.232046362283334</v>
+        <v>82.867628361829105</v>
       </c>
       <c r="N62" s="30">
         <f>'[12]Step 2 WACC LS'!$L$31</f>
-        <v>31.069148068405784</v>
+        <v>75.211005161759758</v>
       </c>
       <c r="O62" s="30">
-        <f>'[12]Step 3 T&amp;S LS'!$L$34</f>
-        <v>54.16528371906864</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>214</v>
       </c>
@@ -14306,18 +14222,17 @@
       </c>
       <c r="M63" s="30">
         <f>'[12]Step 1 LCOE LS'!$G$31* ((1+Inputs!$C$5) ^ (2022-G63))</f>
-        <v>56.8348891342768</v>
+        <v>105.47047113382258</v>
       </c>
       <c r="N63" s="30">
         <f>'[12]Step 2 WACC LS'!$G$31</f>
-        <v>51.583582450093708</v>
+        <v>95.725439543447692</v>
       </c>
       <c r="O63" s="30">
-        <f>'[12]Step 3 T&amp;S LS'!$G$34</f>
-        <v>74.67971810075656</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" hidden="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
         <f>'Study Parameters'!A12</f>
         <v>Fasihi et al. 2019</v>
@@ -14373,7 +14288,7 @@
         <v>292.47958561757542</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>214</v>
       </c>
@@ -14424,7 +14339,7 @@
         <v>292.47958561757542</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>214</v>
       </c>
@@ -14464,18 +14379,17 @@
       </c>
       <c r="M66" s="30">
         <f>'[12]Step 1 LCOE SS'!$L$31* ((1+Inputs!$C$5) ^ (2022-G66))</f>
-        <v>67.513183443189845</v>
+        <v>74.0443735038629</v>
       </c>
       <c r="N66" s="30">
         <f>'[12]Step 2 WACC SS'!$L$31</f>
-        <v>61.275246906565449</v>
+        <v>67.202982248777587</v>
       </c>
       <c r="O66" s="30">
-        <f>'[12]Step 3 T&amp;S SS'!$L$34</f>
-        <v>84.371382557228301</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>214</v>
       </c>
@@ -14515,18 +14429,17 @@
       </c>
       <c r="M67" s="30">
         <f>'[12]Step 1 LCOE SS'!$G$31* ((1+Inputs!$C$5) ^ (2022-G67))</f>
-        <v>86.967988398148719</v>
+        <v>93.490231058162834</v>
       </c>
       <c r="N67" s="30">
         <f>'[12]Step 2 WACC SS'!$G$31</f>
-        <v>78.932509034299216</v>
+        <v>84.85212367835156</v>
       </c>
       <c r="O67" s="30">
-        <f>'[12]Step 3 T&amp;S SS'!$G$34</f>
-        <v>102.02864468496207</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" hidden="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
         <f>'Study Parameters'!A13</f>
         <v>Mazzotti et al. 2013</v>
@@ -14572,7 +14485,7 @@
       </c>
       <c r="M68" s="30"/>
     </row>
-    <row r="69" spans="1:15" hidden="1">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>223</v>
       </c>
@@ -14612,7 +14525,7 @@
       </c>
       <c r="M69" s="30"/>
     </row>
-    <row r="70" spans="1:15" hidden="1">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>223</v>
       </c>
@@ -14652,7 +14565,7 @@
       </c>
       <c r="M70" s="30"/>
     </row>
-    <row r="71" spans="1:15" hidden="1">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
         <f>'Study Parameters'!A14</f>
         <v>Zeman 2014</v>
@@ -14698,7 +14611,7 @@
       </c>
       <c r="M71" s="30"/>
     </row>
-    <row r="72" spans="1:15" hidden="1">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="str">
         <f>'Study Parameters'!A15</f>
         <v>Prats-Salvado et al. 2024</v>
@@ -14746,7 +14659,7 @@
       </c>
       <c r="M72" s="30"/>
     </row>
-    <row r="73" spans="1:15" hidden="1">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>230</v>
       </c>
@@ -14787,7 +14700,7 @@
       </c>
       <c r="M73" s="30"/>
     </row>
-    <row r="74" spans="1:15" hidden="1">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
         <f>'Study Parameters'!A16</f>
         <v>Prats-Salvado et al. 2024</v>
@@ -14834,7 +14747,7 @@
       </c>
       <c r="M74" s="30"/>
     </row>
-    <row r="75" spans="1:15" hidden="1">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>230</v>
       </c>
@@ -14874,7 +14787,7 @@
       </c>
       <c r="M75" s="30"/>
     </row>
-    <row r="76" spans="1:15" hidden="1">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="str">
         <f>'Study Parameters'!A17</f>
         <v>Terlouw et al. 2024</v>
@@ -14920,7 +14833,7 @@
       </c>
       <c r="M76" s="62"/>
     </row>
-    <row r="77" spans="1:15" hidden="1">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>234</v>
       </c>
@@ -14960,7 +14873,7 @@
       </c>
       <c r="M77" s="62"/>
     </row>
-    <row r="78" spans="1:15" hidden="1">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="str">
         <f>'Study Parameters'!A18</f>
         <v>McQueen et al. 2021</v>
@@ -15004,7 +14917,7 @@
         <v>400.60217261536002</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>240</v>
       </c>
@@ -15043,7 +14956,7 @@
         <v>881.5737078159442</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>240</v>
       </c>
@@ -15082,7 +14995,7 @@
         <v>400.60217261536002</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>240</v>
       </c>
@@ -15121,7 +15034,7 @@
         <v>881.5737078159442</v>
       </c>
     </row>
-    <row r="82" spans="1:13" hidden="1">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>240</v>
       </c>
@@ -15160,7 +15073,7 @@
         <v>463.06098024892566</v>
       </c>
     </row>
-    <row r="83" spans="1:13" hidden="1">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>240</v>
       </c>
@@ -15199,7 +15112,7 @@
         <v>558.57147419213493</v>
       </c>
     </row>
-    <row r="84" spans="1:13" hidden="1">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>240</v>
       </c>
@@ -15238,7 +15151,7 @@
         <v>777.69611217374995</v>
       </c>
     </row>
-    <row r="85" spans="1:13" hidden="1">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>240</v>
       </c>
@@ -15277,7 +15190,7 @@
         <v>2052.1001665091567</v>
       </c>
     </row>
-    <row r="86" spans="1:13" hidden="1">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
         <f>'Study Parameters'!A19</f>
         <v>Datta et al. 2023</v>
@@ -15325,7 +15238,7 @@
       </c>
       <c r="M86" s="30"/>
     </row>
-    <row r="87" spans="1:13" hidden="1">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="str">
         <f>'Study Parameters'!A20</f>
         <v>Datta et al. 2023</v>
@@ -15373,7 +15286,7 @@
       </c>
       <c r="M87" s="30"/>
     </row>
-    <row r="88" spans="1:13" hidden="1">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>255</v>
       </c>
@@ -15413,7 +15326,7 @@
       </c>
       <c r="M88" s="30"/>
     </row>
-    <row r="89" spans="1:13" hidden="1">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>255</v>
       </c>
@@ -15453,7 +15366,7 @@
       </c>
       <c r="M89" s="30"/>
     </row>
-    <row r="90" spans="1:13" hidden="1">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>255</v>
       </c>
@@ -15493,7 +15406,7 @@
       </c>
       <c r="M90" s="30"/>
     </row>
-    <row r="91" spans="1:13" hidden="1">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>255</v>
       </c>
@@ -15533,7 +15446,7 @@
       </c>
       <c r="M91" s="30"/>
     </row>
-    <row r="92" spans="1:13" hidden="1">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>255</v>
       </c>
@@ -15573,7 +15486,7 @@
       </c>
       <c r="M92" s="30"/>
     </row>
-    <row r="93" spans="1:13" hidden="1">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>255</v>
       </c>
@@ -15613,7 +15526,7 @@
       </c>
       <c r="M93" s="30"/>
     </row>
-    <row r="94" spans="1:13" hidden="1">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -15653,7 +15566,7 @@
       </c>
       <c r="M94" s="30"/>
     </row>
-    <row r="95" spans="1:13" hidden="1">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>255</v>
       </c>
@@ -15693,7 +15606,7 @@
       </c>
       <c r="M95" s="30"/>
     </row>
-    <row r="96" spans="1:13" hidden="1">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>255</v>
       </c>
@@ -15733,7 +15646,7 @@
       </c>
       <c r="M96" s="30"/>
     </row>
-    <row r="97" spans="1:12" hidden="1">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="str">
         <f>'Study Parameters'!A22</f>
         <v>Simon et al. 2011</v>
@@ -15777,7 +15690,7 @@
         <v>304.707654655694</v>
       </c>
     </row>
-    <row r="98" spans="1:12" hidden="1">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>255</v>
       </c>
@@ -15817,7 +15730,7 @@
         <v>803.14143939193252</v>
       </c>
     </row>
-    <row r="99" spans="1:12" hidden="1">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>255</v>
       </c>
@@ -15857,7 +15770,7 @@
         <v>329.15418006599049</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>267</v>
       </c>
@@ -15895,7 +15808,7 @@
         <v>779.02843503778104</v>
       </c>
     </row>
-    <row r="101" spans="1:12" hidden="1">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>267</v>
       </c>
@@ -15933,7 +15846,7 @@
         <v>831.75510668257198</v>
       </c>
     </row>
-    <row r="102" spans="1:12" hidden="1">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>267</v>
       </c>
@@ -15971,7 +15884,7 @@
         <v>317.24671499539198</v>
       </c>
     </row>
-    <row r="103" spans="1:12" hidden="1">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>267</v>
       </c>
@@ -16009,7 +15922,7 @@
         <v>371.938416568371</v>
       </c>
     </row>
-    <row r="104" spans="1:12" hidden="1">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>267</v>
       </c>
@@ -16047,7 +15960,7 @@
         <v>291.241690193887</v>
       </c>
     </row>
-    <row r="105" spans="1:12" hidden="1">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>267</v>
       </c>
@@ -16085,7 +15998,7 @@
         <v>355.05876736764702</v>
       </c>
     </row>
-    <row r="106" spans="1:12" hidden="1">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>267</v>
       </c>
@@ -16123,7 +16036,7 @@
         <v>267.11083137986202</v>
       </c>
     </row>
-    <row r="107" spans="1:12" hidden="1">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="str">
         <f>'Study Parameters'!A23</f>
         <v>Küng et al. 2023</v>
@@ -16167,7 +16080,7 @@
         <v>314.61251708631102</v>
       </c>
     </row>
-    <row r="108" spans="1:12" hidden="1">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>267</v>
       </c>
@@ -16205,7 +16118,7 @@
         <v>1817.71250053524</v>
       </c>
     </row>
-    <row r="109" spans="1:12" hidden="1">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>267</v>
       </c>
@@ -16243,7 +16156,7 @@
         <v>1990.0315112179401</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>267</v>
       </c>
@@ -16281,7 +16194,7 @@
         <v>980.75097520117902</v>
       </c>
     </row>
-    <row r="111" spans="1:12" hidden="1">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>267</v>
       </c>
@@ -16319,7 +16232,7 @@
         <v>1064.51188379418</v>
       </c>
     </row>
-    <row r="112" spans="1:12" hidden="1">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>267</v>
       </c>
@@ -16357,7 +16270,7 @@
         <v>411.65027432423102</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>267</v>
       </c>
@@ -16395,7 +16308,7 @@
         <v>488.64611354083598</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>267</v>
       </c>
@@ -16433,7 +16346,7 @@
         <v>378.55341271061599</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>267</v>
       </c>
@@ -16471,7 +16384,7 @@
         <v>468.39609948070898</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>267</v>
       </c>
@@ -16509,7 +16422,7 @@
         <v>349.10367628750998</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>267</v>
       </c>
@@ -16547,7 +16460,7 @@
         <v>415.97729787873197</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>267</v>
       </c>
@@ -16585,7 +16498,7 @@
         <v>2476.9733161530498</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>267</v>
       </c>
@@ -16623,7 +16536,7 @@
         <v>2750.7170677000299</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="str">
         <f>'Study Parameters'!A24</f>
         <v>Küng et al. 2023</v>
@@ -16666,7 +16579,7 @@
         <v>183.15040372394199</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>267</v>
       </c>
@@ -16704,7 +16617,7 @@
         <v>227.07677281852301</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>267</v>
       </c>
@@ -16742,7 +16655,7 @@
         <v>61.893630816227301</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>267</v>
       </c>
@@ -16780,7 +16693,7 @@
         <v>72.225103599114604</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>267</v>
       </c>
@@ -16818,7 +16731,7 @@
         <v>393.65606020680502</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -16856,7 +16769,7 @@
         <v>503.939346853232</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>267</v>
       </c>
@@ -16894,7 +16807,7 @@
         <v>406.913082895564</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>267</v>
       </c>
@@ -16932,7 +16845,7 @@
         <v>517.19636954199098</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>267</v>
       </c>
@@ -16970,7 +16883,7 @@
         <v>243.248532930187</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>267</v>
       </c>
@@ -17008,7 +16921,7 @@
         <v>305.088767461244</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>267</v>
       </c>
@@ -17046,7 +16959,7 @@
         <v>76.028698179975393</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>267</v>
       </c>
@@ -17084,7 +16997,7 @@
         <v>90.573508350133693</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>267</v>
       </c>
@@ -17122,7 +17035,7 @@
         <v>523.47869237559496</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>267</v>
       </c>
@@ -17160,7 +17073,7 @@
         <v>698.67329510641696</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -17198,7 +17111,7 @@
         <v>536.73571506435496</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>267</v>
       </c>
@@ -17236,7 +17149,7 @@
         <v>711.93031779517605</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="str">
         <f>'Study Parameters'!A25</f>
         <v>Mostafa et al. 2022</v>
@@ -17262,7 +17175,7 @@
       </c>
       <c r="L136" s="30"/>
     </row>
-    <row r="137" spans="1:15" hidden="1">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="str">
         <f>'Study Parameters'!A26</f>
         <v>Keith et al. 2018</v>
@@ -17319,7 +17232,7 @@
         <v>295.67151321600323</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -17367,7 +17280,7 @@
         <v>238.63022727495593</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>275</v>
       </c>
@@ -17415,7 +17328,7 @@
         <v>224.78482396902055</v>
       </c>
     </row>
-    <row r="140" spans="1:15">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>275</v>
       </c>
@@ -17452,18 +17365,17 @@
       </c>
       <c r="M140" s="30">
         <f>'[21]Step 1 LCOE - EE'!$F$24*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>127.68430518730926</v>
+        <v>130.30491652206067</v>
       </c>
       <c r="N140" s="30">
         <f>'[21]Step 2 WACC'!$F$24*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>136.57580542513767</v>
+        <v>139.1964167598891</v>
       </c>
       <c r="O140" s="30">
-        <f>'[21]Step 3 T&amp;S'!$F$27*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>165.48894707561087</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" hidden="1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>275</v>
       </c>
@@ -17514,7 +17426,7 @@
         <v>295.67151321600323</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>275</v>
       </c>
@@ -17565,7 +17477,7 @@
         <v>238.63022727495593</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>275</v>
       </c>
@@ -17616,7 +17528,7 @@
         <v>224.78482396902055</v>
       </c>
     </row>
-    <row r="144" spans="1:15">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>275</v>
       </c>
@@ -17653,18 +17565,17 @@
       </c>
       <c r="M144" s="30">
         <f>'[21]Step 1 LCOE - EE (2)'!$F$24* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>168.83296284775582</v>
+        <v>171.45357418250728</v>
       </c>
       <c r="N144" s="30">
         <f>'[21]Step 2 WACC (2)'!$F$24* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>136.57580542513767</v>
+        <v>139.1964167598891</v>
       </c>
       <c r="O144" s="30">
-        <f>'[21]Step 3 T&amp;S (2)'!$F$27* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>165.48894707561087</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" hidden="1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="str">
         <f>'Study Parameters'!A27</f>
         <v>Gray et al. 2024</v>
@@ -17718,7 +17629,7 @@
         <v>1422.4526421724208</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="str">
         <f>'Study Parameters'!A28</f>
         <v>Rosen et al. 2024</v>
@@ -17751,7 +17662,7 @@
       </c>
       <c r="L146" s="30"/>
     </row>
-    <row r="147" spans="1:15" hidden="1">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="str">
         <f>'Study Parameters'!A29</f>
         <v>Rosen et al. 2024</v>
@@ -17784,7 +17695,7 @@
       </c>
       <c r="L147" s="30"/>
     </row>
-    <row r="148" spans="1:15" hidden="1">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="str">
         <f>'Study Parameters'!A30</f>
         <v>Rosen et al. 2024</v>
@@ -17817,7 +17728,7 @@
       </c>
       <c r="L148" s="30"/>
     </row>
-    <row r="149" spans="1:15" hidden="1">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="str">
         <f>'Study Parameters'!A31</f>
         <v>Rosen et al. 2024</v>
@@ -17850,7 +17761,7 @@
       </c>
       <c r="L149" s="30"/>
     </row>
-    <row r="150" spans="1:15" hidden="1">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="str">
         <f>'Study Parameters'!A32</f>
         <v>Sabatino et al. 2020</v>
@@ -17877,7 +17788,7 @@
       </c>
       <c r="L150" s="30"/>
     </row>
-    <row r="151" spans="1:15" hidden="1">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="str">
         <f>'Study Parameters'!A33</f>
         <v>McQueen et al. 2020c</v>
@@ -17919,7 +17830,7 @@
         <v>52.859259278213045</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="str">
         <f>'Study Parameters'!A33</f>
         <v>McQueen et al. 2020c</v>
@@ -17960,7 +17871,7 @@
         <v>174.22096158203897</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>294</v>
       </c>
@@ -17996,7 +17907,7 @@
         <v>45.162595126533958</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>294</v>
       </c>
@@ -18032,7 +17943,7 @@
         <v>155.30185025856494</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="str">
         <f>'Study Parameters'!A34</f>
         <v>Lee et al. 2023</v>
@@ -18090,7 +18001,7 @@
         <v>270.09276004403995</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="str">
         <f>'Study Parameters'!A35</f>
         <v>Abanades et al. 2023</v>
@@ -18117,7 +18028,7 @@
       </c>
       <c r="L156" s="30"/>
     </row>
-    <row r="157" spans="1:15" hidden="1">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="str">
         <f>'Study Parameters'!A36</f>
         <v>Abanades et al. 2020</v>
@@ -18144,7 +18055,7 @@
       </c>
       <c r="L157" s="30"/>
     </row>
-    <row r="158" spans="1:15" hidden="1">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="str">
         <f>'Study Parameters'!A37</f>
         <v>Ragipani et al. 2022</v>
@@ -18186,7 +18097,7 @@
         <v>121.14570202833102</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>315</v>
       </c>
@@ -18222,7 +18133,7 @@
         <v>140.09669470231475</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>329</v>
       </c>
@@ -18270,7 +18181,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>329</v>
       </c>
@@ -18318,7 +18229,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>329</v>
       </c>
@@ -18366,7 +18277,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="163" spans="1:15">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" t="str">
         <f>'Study Parameters'!A39</f>
         <v>Pett-Ridge et al. 2024</v>
@@ -18407,18 +18318,17 @@
       </c>
       <c r="M163" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>118.45853215160149</v>
+        <v>134.11219617439485</v>
       </c>
       <c r="N163" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>106.84340810280642</v>
+        <v>122.49707212559984</v>
       </c>
       <c r="O163" s="30">
-        <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>131.84340810280642</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>329</v>
       </c>
@@ -18455,18 +18365,17 @@
       </c>
       <c r="M164" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>118.45853215160149</v>
+        <v>134.11219617439485</v>
       </c>
       <c r="N164" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>106.84340810280642</v>
+        <v>122.49707212559984</v>
       </c>
       <c r="O164" s="30">
-        <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>131.84340810280642</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>329</v>
       </c>
@@ -18503,18 +18412,17 @@
       </c>
       <c r="M165" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>118.45853215160149</v>
+        <v>134.11219617439485</v>
       </c>
       <c r="N165" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>106.84340810280642</v>
+        <v>122.49707212559984</v>
       </c>
       <c r="O165" s="30">
-        <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>131.84340810280642</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15" hidden="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="str">
         <f>'Study Parameters'!A40</f>
         <v>Pett-Ridge et al. 2024</v>
@@ -18567,7 +18475,7 @@
         <v>440.01216847304312</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>329</v>
       </c>
@@ -18615,7 +18523,7 @@
         <v>339.04143355290654</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>329</v>
       </c>
@@ -18663,7 +18571,7 @@
         <v>263.41019772115243</v>
       </c>
     </row>
-    <row r="169" spans="1:15">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>329</v>
       </c>
@@ -18697,18 +18605,17 @@
       </c>
       <c r="M169" s="30">
         <f>'[27]Step 1 - LCOE + EE'!$G$23</f>
-        <v>136.97848574432413</v>
+        <v>139.37212947003994</v>
       </c>
       <c r="N169" s="30">
         <f>'[27]Step 2 - WACC'!$G$23</f>
-        <v>136.97848574432413</v>
+        <v>139.37212947003994</v>
       </c>
       <c r="O169" s="30">
-        <f>'[27]Step 3 - T&amp;S'!$G$23</f>
-        <v>161.3365262382693</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" hidden="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="str">
         <f>'Study Parameters'!A41</f>
         <v>NETL/Valentine 2022a</v>
@@ -18754,7 +18661,7 @@
       </c>
       <c r="M170" s="30"/>
     </row>
-    <row r="171" spans="1:15" hidden="1">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>336</v>
       </c>
@@ -18794,7 +18701,7 @@
       </c>
       <c r="M171" s="30"/>
     </row>
-    <row r="172" spans="1:15" hidden="1">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>336</v>
       </c>
@@ -18834,7 +18741,7 @@
       </c>
       <c r="M172" s="30"/>
     </row>
-    <row r="173" spans="1:15" hidden="1">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="str">
         <f>'Study Parameters'!A42</f>
         <v>NETL/Valentine 2022b</v>
@@ -18880,7 +18787,7 @@
       </c>
       <c r="M173" s="30"/>
     </row>
-    <row r="174" spans="1:15" hidden="1">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>342</v>
       </c>
@@ -18920,7 +18827,7 @@
       </c>
       <c r="M174" s="30"/>
     </row>
-    <row r="175" spans="1:15" hidden="1">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>342</v>
       </c>
@@ -18960,7 +18867,7 @@
       </c>
       <c r="M175" s="30"/>
     </row>
-    <row r="176" spans="1:15" hidden="1">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="str">
         <f>'Study Parameters'!A43</f>
         <v>NASEM 2019</v>
@@ -18987,7 +18894,7 @@
       </c>
       <c r="L176" s="30"/>
     </row>
-    <row r="177" spans="1:13" hidden="1">
+    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -19014,7 +18921,7 @@
       </c>
       <c r="L177" s="30"/>
     </row>
-    <row r="178" spans="1:13" hidden="1">
+    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -19041,7 +18948,7 @@
       </c>
       <c r="L178" s="30"/>
     </row>
-    <row r="179" spans="1:13" hidden="1">
+    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="str">
         <f>'Study Parameters'!A45</f>
         <v>APS 2011</v>
@@ -19087,7 +18994,7 @@
       </c>
       <c r="M179" s="30"/>
     </row>
-    <row r="180" spans="1:13" hidden="1">
+    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>348</v>
       </c>
@@ -19149,14 +19056,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08C0257C-D407-4235-8443-42A5A3A9A73A}">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.09765625" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="63" t="s">
         <v>751</v>
       </c>
@@ -19166,7 +19073,7 @@
       <c r="J1" s="74"/>
       <c r="K1" s="74"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="64" t="s">
         <v>753</v>
       </c>
@@ -19176,7 +19083,7 @@
       <c r="J2" s="74"/>
       <c r="K2" s="74"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="64"/>
       <c r="F3" s="74" t="s">
         <v>755</v>
@@ -19184,7 +19091,7 @@
       <c r="J3" s="74"/>
       <c r="K3" s="74"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>756</v>
       </c>
@@ -19200,7 +19107,7 @@
       <c r="J4" s="74"/>
       <c r="K4" s="74"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>760</v>
       </c>
@@ -19216,7 +19123,7 @@
       <c r="J5" s="74"/>
       <c r="K5" s="74"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>764</v>
       </c>
@@ -19229,7 +19136,7 @@
       <c r="J6" s="74"/>
       <c r="K6" s="74"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>766</v>
       </c>
@@ -19239,7 +19146,7 @@
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>767</v>
       </c>
@@ -19249,7 +19156,7 @@
       <c r="J8" s="74"/>
       <c r="K8" s="74"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>768</v>
       </c>
@@ -19259,7 +19166,7 @@
       <c r="J9" s="74"/>
       <c r="K9" s="74"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>769</v>
       </c>
@@ -19269,7 +19176,7 @@
       <c r="J10" s="74"/>
       <c r="K10" s="74"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>770</v>
       </c>
@@ -19279,7 +19186,7 @@
       <c r="J11" s="74"/>
       <c r="K11" s="74"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>771</v>
       </c>
@@ -19289,7 +19196,7 @@
       <c r="J12" s="76"/>
       <c r="K12" s="77"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>772</v>
       </c>
@@ -19299,7 +19206,7 @@
       <c r="J13" s="76"/>
       <c r="K13" s="75"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>773</v>
       </c>
@@ -19309,7 +19216,7 @@
       <c r="J14" s="76"/>
       <c r="K14" s="77"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>774</v>
       </c>
@@ -19319,7 +19226,7 @@
       <c r="J15" s="76"/>
       <c r="K15" s="77"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>775</v>
       </c>
@@ -19329,7 +19236,7 @@
       <c r="J16" s="76"/>
       <c r="K16" s="77"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>776</v>
       </c>
@@ -19339,7 +19246,7 @@
       <c r="J17" s="76"/>
       <c r="K17" s="77"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>777</v>
       </c>
@@ -19349,7 +19256,7 @@
       <c r="J18" s="76"/>
       <c r="K18" s="77"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>778</v>
       </c>
@@ -19359,7 +19266,7 @@
       <c r="J19" s="76"/>
       <c r="K19" s="74"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>779</v>
       </c>
@@ -19369,7 +19276,7 @@
       <c r="J20" s="76"/>
       <c r="K20" s="77"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>780</v>
       </c>
@@ -19379,7 +19286,7 @@
       <c r="J21" s="76"/>
       <c r="K21" s="77"/>
     </row>
-    <row r="22" spans="1:11" ht="16.149999999999999" thickBot="1">
+    <row r="22" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>96</v>
       </c>
@@ -19390,7 +19297,7 @@
       <c r="J22" s="76"/>
       <c r="K22" s="77"/>
     </row>
-    <row r="23" spans="1:11" ht="18.600000000000001" thickBot="1">
+    <row r="23" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="85" t="s">
         <v>80</v>
       </c>
@@ -19421,7 +19328,7 @@
       <c r="J23" s="76"/>
       <c r="K23" s="77"/>
     </row>
-    <row r="24" spans="1:11" ht="16.149999999999999" thickBot="1">
+    <row r="24" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="78" t="s">
         <v>782</v>
       </c>
@@ -19452,14 +19359,14 @@
       <c r="J24" s="76"/>
       <c r="K24" s="77"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="86" t="s">
         <v>784</v>
       </c>
       <c r="J25" s="76"/>
       <c r="K25" s="77"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>785</v>
       </c>
@@ -19473,7 +19380,7 @@
       <c r="J26" s="76"/>
       <c r="K26" s="77"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -19496,52 +19403,52 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56965C59-6106-408A-A712-D0B6552D4011}">
   <dimension ref="A1:B211"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="74" t="s">
         <v>752</v>
       </c>
       <c r="B1" s="74"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="74" t="s">
         <v>754</v>
       </c>
       <c r="B2" s="74"/>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="74" t="s">
         <v>755</v>
       </c>
       <c r="B3" s="74"/>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="74" t="s">
         <v>759</v>
       </c>
       <c r="B4" s="74"/>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="74" t="s">
         <v>763</v>
       </c>
       <c r="B5" s="74"/>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="74" t="s">
         <v>765</v>
       </c>
       <c r="B6" s="74"/>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="74"/>
       <c r="B7" s="74"/>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="74" t="s">
         <v>788</v>
       </c>
@@ -19549,17 +19456,17 @@
         <v>789</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="74"/>
       <c r="B9" s="74"/>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
         <v>790</v>
       </c>
       <c r="B10" s="74"/>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="74" t="s">
         <v>791</v>
       </c>
@@ -19567,7 +19474,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="76">
         <v>39448</v>
       </c>
@@ -19575,7 +19482,7 @@
         <v>1.4728000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="76">
         <v>39479</v>
       </c>
@@ -19583,7 +19490,7 @@
         <v>1.4759</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="76">
         <v>39508</v>
       </c>
@@ -19591,7 +19498,7 @@
         <v>1.552</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="76">
         <v>39539</v>
       </c>
@@ -19599,7 +19506,7 @@
         <v>1.5753999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="76">
         <v>39569</v>
       </c>
@@ -19607,7 +19514,7 @@
         <v>1.5553999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="76">
         <v>39600</v>
       </c>
@@ -19615,7 +19522,7 @@
         <v>1.5562</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="76">
         <v>39630</v>
       </c>
@@ -19623,7 +19530,7 @@
         <v>1.5759000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="76">
         <v>39661</v>
       </c>
@@ -19631,7 +19538,7 @@
         <v>1.4955000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="76">
         <v>39692</v>
       </c>
@@ -19639,7 +19546,7 @@
         <v>1.4341999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="76">
         <v>39722</v>
       </c>
@@ -19647,7 +19554,7 @@
         <v>1.3266</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="76">
         <v>39753</v>
       </c>
@@ -19655,7 +19562,7 @@
         <v>1.2744</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="76">
         <v>39783</v>
       </c>
@@ -19663,7 +19570,7 @@
         <v>1.3511</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="76">
         <v>39814</v>
       </c>
@@ -19671,7 +19578,7 @@
         <v>1.3244</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="76">
         <v>39845</v>
       </c>
@@ -19679,7 +19586,7 @@
         <v>1.2797000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="76">
         <v>39873</v>
       </c>
@@ -19687,7 +19594,7 @@
         <v>1.3049999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="76">
         <v>39904</v>
       </c>
@@ -19695,7 +19602,7 @@
         <v>1.3199000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="76">
         <v>39934</v>
       </c>
@@ -19703,7 +19610,7 @@
         <v>1.3646</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="76">
         <v>39965</v>
       </c>
@@ -19711,7 +19618,7 @@
         <v>1.4014</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="76">
         <v>39995</v>
       </c>
@@ -19719,7 +19626,7 @@
         <v>1.4092</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="76">
         <v>40026</v>
       </c>
@@ -19727,7 +19634,7 @@
         <v>1.4266000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="76">
         <v>40057</v>
       </c>
@@ -19735,7 +19642,7 @@
         <v>1.4575</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="76">
         <v>40087</v>
       </c>
@@ -19743,7 +19650,7 @@
         <v>1.4821</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="76">
         <v>40118</v>
       </c>
@@ -19751,7 +19658,7 @@
         <v>1.4907999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="76">
         <v>40148</v>
       </c>
@@ -19759,7 +19666,7 @@
         <v>1.4579</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="76">
         <v>40179</v>
       </c>
@@ -19767,7 +19674,7 @@
         <v>1.4266000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="76">
         <v>40210</v>
       </c>
@@ -19775,7 +19682,7 @@
         <v>1.3680000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="76">
         <v>40238</v>
       </c>
@@ -19783,7 +19690,7 @@
         <v>1.357</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="76">
         <v>40269</v>
       </c>
@@ -19791,7 +19698,7 @@
         <v>1.3416999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="76">
         <v>40299</v>
       </c>
@@ -19799,7 +19706,7 @@
         <v>1.2563</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="76">
         <v>40330</v>
       </c>
@@ -19807,7 +19714,7 @@
         <v>1.2222999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="76">
         <v>40360</v>
       </c>
@@ -19815,7 +19722,7 @@
         <v>1.2810999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="76">
         <v>40391</v>
       </c>
@@ -19823,7 +19730,7 @@
         <v>1.2903</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="76">
         <v>40422</v>
       </c>
@@ -19831,7 +19738,7 @@
         <v>1.3103</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="76">
         <v>40452</v>
       </c>
@@ -19839,7 +19746,7 @@
         <v>1.3900999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="76">
         <v>40483</v>
       </c>
@@ -19847,7 +19754,7 @@
         <v>1.3653999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="76">
         <v>40513</v>
       </c>
@@ -19855,7 +19762,7 @@
         <v>1.3221000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="76">
         <v>40544</v>
       </c>
@@ -19863,7 +19770,7 @@
         <v>1.3371</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="76">
         <v>40575</v>
       </c>
@@ -19871,7 +19778,7 @@
         <v>1.3655999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="76">
         <v>40603</v>
       </c>
@@ -19879,7 +19786,7 @@
         <v>1.4019999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="76">
         <v>40634</v>
       </c>
@@ -19887,7 +19794,7 @@
         <v>1.446</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="76">
         <v>40664</v>
       </c>
@@ -19895,7 +19802,7 @@
         <v>1.4335</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="76">
         <v>40695</v>
       </c>
@@ -19903,7 +19810,7 @@
         <v>1.4402999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="76">
         <v>40725</v>
       </c>
@@ -19911,7 +19818,7 @@
         <v>1.4275</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="76">
         <v>40756</v>
       </c>
@@ -19919,7 +19826,7 @@
         <v>1.4333</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="76">
         <v>40787</v>
       </c>
@@ -19927,7 +19834,7 @@
         <v>1.3747</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="76">
         <v>40817</v>
       </c>
@@ -19935,7 +19842,7 @@
         <v>1.3732</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="76">
         <v>40848</v>
       </c>
@@ -19943,7 +19850,7 @@
         <v>1.3557999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="76">
         <v>40878</v>
       </c>
@@ -19951,7 +19858,7 @@
         <v>1.3154999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="76">
         <v>40909</v>
       </c>
@@ -19959,7 +19866,7 @@
         <v>1.2909999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="76">
         <v>40940</v>
       </c>
@@ -19967,7 +19874,7 @@
         <v>1.3238000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="76">
         <v>40969</v>
       </c>
@@ -19975,7 +19882,7 @@
         <v>1.3208</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="76">
         <v>41000</v>
       </c>
@@ -19983,7 +19890,7 @@
         <v>1.3160000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="76">
         <v>41030</v>
       </c>
@@ -19991,7 +19898,7 @@
         <v>1.2806</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="76">
         <v>41061</v>
       </c>
@@ -19999,7 +19906,7 @@
         <v>1.2541</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="76">
         <v>41091</v>
       </c>
@@ -20007,7 +19914,7 @@
         <v>1.2278</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="76">
         <v>41122</v>
       </c>
@@ -20015,7 +19922,7 @@
         <v>1.2405999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="76">
         <v>41153</v>
       </c>
@@ -20023,7 +19930,7 @@
         <v>1.2885</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="76">
         <v>41183</v>
       </c>
@@ -20031,7 +19938,7 @@
         <v>1.2974000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="76">
         <v>41214</v>
       </c>
@@ -20039,7 +19946,7 @@
         <v>1.2837000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="76">
         <v>41244</v>
       </c>
@@ -20047,7 +19954,7 @@
         <v>1.3119000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="76">
         <v>41275</v>
       </c>
@@ -20055,7 +19962,7 @@
         <v>1.3304</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="76">
         <v>41306</v>
       </c>
@@ -20063,7 +19970,7 @@
         <v>1.3347</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="76">
         <v>41334</v>
       </c>
@@ -20071,7 +19978,7 @@
         <v>1.2952999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="76">
         <v>41365</v>
       </c>
@@ -20079,7 +19986,7 @@
         <v>1.3025</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="76">
         <v>41395</v>
       </c>
@@ -20087,7 +19994,7 @@
         <v>1.2983</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="76">
         <v>41426</v>
       </c>
@@ -20095,7 +20002,7 @@
         <v>1.3197000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="76">
         <v>41456</v>
       </c>
@@ -20103,7 +20010,7 @@
         <v>1.3088</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="76">
         <v>41487</v>
       </c>
@@ -20111,7 +20018,7 @@
         <v>1.3313999999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="76">
         <v>41518</v>
       </c>
@@ -20119,7 +20026,7 @@
         <v>1.3364</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="76">
         <v>41548</v>
       </c>
@@ -20127,7 +20034,7 @@
         <v>1.3646</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="76">
         <v>41579</v>
       </c>
@@ -20135,7 +20042,7 @@
         <v>1.3491</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="76">
         <v>41609</v>
       </c>
@@ -20143,7 +20050,7 @@
         <v>1.3708</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="76">
         <v>41640</v>
       </c>
@@ -20151,7 +20058,7 @@
         <v>1.3617999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="76">
         <v>41671</v>
       </c>
@@ -20159,7 +20066,7 @@
         <v>1.3665</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="76">
         <v>41699</v>
       </c>
@@ -20167,7 +20074,7 @@
         <v>1.3828</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="76">
         <v>41730</v>
       </c>
@@ -20175,7 +20082,7 @@
         <v>1.381</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="76">
         <v>41760</v>
       </c>
@@ -20183,7 +20090,7 @@
         <v>1.3738999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="76">
         <v>41791</v>
       </c>
@@ -20191,7 +20098,7 @@
         <v>1.3594999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="76">
         <v>41821</v>
       </c>
@@ -20199,7 +20106,7 @@
         <v>1.3532999999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="76">
         <v>41852</v>
       </c>
@@ -20207,7 +20114,7 @@
         <v>1.3314999999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="76">
         <v>41883</v>
       </c>
@@ -20215,7 +20122,7 @@
         <v>1.2888999999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="76">
         <v>41913</v>
       </c>
@@ -20223,7 +20130,7 @@
         <v>1.2677</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="76">
         <v>41944</v>
       </c>
@@ -20231,7 +20138,7 @@
         <v>1.2473000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="76">
         <v>41974</v>
       </c>
@@ -20239,7 +20146,7 @@
         <v>1.2329000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="76">
         <v>42005</v>
       </c>
@@ -20247,7 +20154,7 @@
         <v>1.1615</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="76">
         <v>42036</v>
       </c>
@@ -20255,7 +20162,7 @@
         <v>1.135</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="76">
         <v>42064</v>
       </c>
@@ -20263,7 +20170,7 @@
         <v>1.0819000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="76">
         <v>42095</v>
       </c>
@@ -20271,7 +20178,7 @@
         <v>1.0822000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="76">
         <v>42125</v>
       </c>
@@ -20279,7 +20186,7 @@
         <v>1.1167</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="76">
         <v>42156</v>
       </c>
@@ -20287,7 +20194,7 @@
         <v>1.1226</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="76">
         <v>42186</v>
       </c>
@@ -20295,7 +20202,7 @@
         <v>1.0996999999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="76">
         <v>42217</v>
       </c>
@@ -20303,7 +20210,7 @@
         <v>1.1135999999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="76">
         <v>42248</v>
       </c>
@@ -20311,7 +20218,7 @@
         <v>1.1229</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="76">
         <v>42278</v>
       </c>
@@ -20319,7 +20226,7 @@
         <v>1.1228</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="76">
         <v>42309</v>
       </c>
@@ -20327,7 +20234,7 @@
         <v>1.0727</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="76">
         <v>42339</v>
       </c>
@@ -20335,7 +20242,7 @@
         <v>1.0889</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="76">
         <v>42370</v>
       </c>
@@ -20343,7 +20250,7 @@
         <v>1.0854999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="76">
         <v>42401</v>
       </c>
@@ -20351,7 +20258,7 @@
         <v>1.1092</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="76">
         <v>42430</v>
       </c>
@@ -20359,7 +20266,7 @@
         <v>1.1133999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="76">
         <v>42461</v>
       </c>
@@ -20367,7 +20274,7 @@
         <v>1.1346000000000001</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="76">
         <v>42491</v>
       </c>
@@ -20375,7 +20282,7 @@
         <v>1.1312</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="76">
         <v>42522</v>
       </c>
@@ -20383,7 +20290,7 @@
         <v>1.1232</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="76">
         <v>42552</v>
       </c>
@@ -20391,7 +20298,7 @@
         <v>1.1054999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="76">
         <v>42583</v>
       </c>
@@ -20399,7 +20306,7 @@
         <v>1.1207</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="76">
         <v>42614</v>
       </c>
@@ -20407,7 +20314,7 @@
         <v>1.1217999999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="76">
         <v>42644</v>
       </c>
@@ -20415,7 +20322,7 @@
         <v>1.1013999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="76">
         <v>42675</v>
       </c>
@@ -20423,7 +20330,7 @@
         <v>1.0791999999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="76">
         <v>42705</v>
       </c>
@@ -20431,7 +20338,7 @@
         <v>1.0545</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="76">
         <v>42736</v>
       </c>
@@ -20439,7 +20346,7 @@
         <v>1.0634999999999999</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="76">
         <v>42767</v>
       </c>
@@ -20447,7 +20354,7 @@
         <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="76">
         <v>42795</v>
       </c>
@@ -20455,7 +20362,7 @@
         <v>1.0690999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="76">
         <v>42826</v>
       </c>
@@ -20463,7 +20370,7 @@
         <v>1.0713999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="76">
         <v>42856</v>
       </c>
@@ -20471,7 +20378,7 @@
         <v>1.105</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="76">
         <v>42887</v>
       </c>
@@ -20479,7 +20386,7 @@
         <v>1.1233</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="76">
         <v>42917</v>
       </c>
@@ -20487,7 +20394,7 @@
         <v>1.153</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="76">
         <v>42948</v>
       </c>
@@ -20495,7 +20402,7 @@
         <v>1.1813</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="76">
         <v>42979</v>
       </c>
@@ -20503,7 +20410,7 @@
         <v>1.1913</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="76">
         <v>43009</v>
       </c>
@@ -20511,7 +20418,7 @@
         <v>1.1755</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="76">
         <v>43040</v>
       </c>
@@ -20519,7 +20426,7 @@
         <v>1.1742999999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="76">
         <v>43070</v>
       </c>
@@ -20527,7 +20434,7 @@
         <v>1.1836</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="76">
         <v>43101</v>
       </c>
@@ -20535,7 +20442,7 @@
         <v>1.2197</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="76">
         <v>43132</v>
       </c>
@@ -20543,7 +20450,7 @@
         <v>1.234</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="76">
         <v>43160</v>
       </c>
@@ -20551,7 +20458,7 @@
         <v>1.2334000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="76">
         <v>43191</v>
       </c>
@@ -20559,7 +20466,7 @@
         <v>1.2270000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="76">
         <v>43221</v>
       </c>
@@ -20567,7 +20474,7 @@
         <v>1.1822999999999999</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="76">
         <v>43252</v>
       </c>
@@ -20575,7 +20482,7 @@
         <v>1.1678999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="76">
         <v>43282</v>
       </c>
@@ -20583,7 +20490,7 @@
         <v>1.1685000000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="76">
         <v>43313</v>
       </c>
@@ -20591,7 +20498,7 @@
         <v>1.1547000000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="76">
         <v>43344</v>
       </c>
@@ -20599,7 +20506,7 @@
         <v>1.1667000000000001</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="76">
         <v>43374</v>
       </c>
@@ -20607,7 +20514,7 @@
         <v>1.1488</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="76">
         <v>43405</v>
       </c>
@@ -20615,7 +20522,7 @@
         <v>1.1364000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="76">
         <v>43435</v>
       </c>
@@ -20623,7 +20530,7 @@
         <v>1.1379999999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="76">
         <v>43466</v>
       </c>
@@ -20631,7 +20538,7 @@
         <v>1.1417999999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="76">
         <v>43497</v>
       </c>
@@ -20639,7 +20546,7 @@
         <v>1.1349</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="76">
         <v>43525</v>
       </c>
@@ -20647,7 +20554,7 @@
         <v>1.1295999999999999</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="76">
         <v>43556</v>
       </c>
@@ -20655,7 +20562,7 @@
         <v>1.1234</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="76">
         <v>43586</v>
       </c>
@@ -20663,7 +20570,7 @@
         <v>1.1187</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="76">
         <v>43617</v>
       </c>
@@ -20671,7 +20578,7 @@
         <v>1.1294999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="76">
         <v>43647</v>
       </c>
@@ -20679,7 +20586,7 @@
         <v>1.1211</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="76">
         <v>43678</v>
       </c>
@@ -20687,7 +20594,7 @@
         <v>1.1129</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="76">
         <v>43709</v>
       </c>
@@ -20695,7 +20602,7 @@
         <v>1.1011</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="76">
         <v>43739</v>
       </c>
@@ -20703,7 +20610,7 @@
         <v>1.1057999999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="76">
         <v>43770</v>
       </c>
@@ -20711,7 +20618,7 @@
         <v>1.1051</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="76">
         <v>43800</v>
       </c>
@@ -20719,7 +20626,7 @@
         <v>1.1113999999999999</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="76">
         <v>43831</v>
       </c>
@@ -20727,7 +20634,7 @@
         <v>1.1097999999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="76">
         <v>43862</v>
       </c>
@@ -20735,7 +20642,7 @@
         <v>1.0911</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="76">
         <v>43891</v>
       </c>
@@ -20743,7 +20650,7 @@
         <v>1.1046</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="76">
         <v>43922</v>
       </c>
@@ -20751,7 +20658,7 @@
         <v>1.0871</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="76">
         <v>43952</v>
       </c>
@@ -20759,7 +20666,7 @@
         <v>1.0907</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="76">
         <v>43983</v>
       </c>
@@ -20767,7 +20674,7 @@
         <v>1.1258999999999999</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="76">
         <v>44013</v>
       </c>
@@ -20775,7 +20682,7 @@
         <v>1.1488</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="76">
         <v>44044</v>
       </c>
@@ -20783,7 +20690,7 @@
         <v>1.1831</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="76">
         <v>44075</v>
       </c>
@@ -20791,7 +20698,7 @@
         <v>1.1785000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="76">
         <v>44105</v>
       </c>
@@ -20799,7 +20706,7 @@
         <v>1.1768000000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="76">
         <v>44136</v>
       </c>
@@ -20807,7 +20714,7 @@
         <v>1.1826000000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="76">
         <v>44166</v>
       </c>
@@ -20815,7 +20722,7 @@
         <v>1.2168000000000001</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="76">
         <v>44197</v>
       </c>
@@ -20823,7 +20730,7 @@
         <v>1.2178</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="76">
         <v>44228</v>
       </c>
@@ -20831,7 +20738,7 @@
         <v>1.2094</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="76">
         <v>44256</v>
       </c>
@@ -20839,7 +20746,7 @@
         <v>1.1901999999999999</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="76">
         <v>44287</v>
       </c>
@@ -20847,7 +20754,7 @@
         <v>1.1964999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="76">
         <v>44317</v>
       </c>
@@ -20855,7 +20762,7 @@
         <v>1.2145999999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="76">
         <v>44348</v>
       </c>
@@ -20863,7 +20770,7 @@
         <v>1.2048000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="76">
         <v>44378</v>
       </c>
@@ -20871,7 +20778,7 @@
         <v>1.1820999999999999</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="76">
         <v>44409</v>
       </c>
@@ -20879,7 +20786,7 @@
         <v>1.1767000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="76">
         <v>44440</v>
       </c>
@@ -20887,7 +20794,7 @@
         <v>1.1765000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="76">
         <v>44470</v>
       </c>
@@ -20895,7 +20802,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="76">
         <v>44501</v>
       </c>
@@ -20903,7 +20810,7 @@
         <v>1.1415999999999999</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="76">
         <v>44531</v>
       </c>
@@ -20911,7 +20818,7 @@
         <v>1.1301000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="76">
         <v>44562</v>
       </c>
@@ -20919,7 +20826,7 @@
         <v>1.1316999999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="76">
         <v>44593</v>
       </c>
@@ -20927,7 +20834,7 @@
         <v>1.1349</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="76">
         <v>44621</v>
       </c>
@@ -20935,7 +20842,7 @@
         <v>1.1019000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="76">
         <v>44652</v>
       </c>
@@ -20943,7 +20850,7 @@
         <v>1.0803</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="76">
         <v>44682</v>
       </c>
@@ -20951,7 +20858,7 @@
         <v>1.0567</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="76">
         <v>44713</v>
       </c>
@@ -20959,7 +20866,7 @@
         <v>1.0567</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="76">
         <v>44743</v>
       </c>
@@ -20967,7 +20874,7 @@
         <v>1.0167999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="76">
         <v>44774</v>
       </c>
@@ -20975,7 +20882,7 @@
         <v>1.0128999999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="76">
         <v>44805</v>
       </c>
@@ -20983,7 +20890,7 @@
         <v>0.9899</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="76">
         <v>44835</v>
       </c>
@@ -20991,7 +20898,7 @@
         <v>0.98529999999999995</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="76">
         <v>44866</v>
       </c>
@@ -20999,7 +20906,7 @@
         <v>1.0192000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="76">
         <v>44896</v>
       </c>
@@ -21007,7 +20914,7 @@
         <v>1.0590999999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="76">
         <v>44927</v>
       </c>
@@ -21015,7 +20922,7 @@
         <v>1.0777000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="76">
         <v>44958</v>
       </c>
@@ -21023,7 +20930,7 @@
         <v>1.0702</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="76">
         <v>44986</v>
       </c>
@@ -21031,7 +20938,7 @@
         <v>1.0710999999999999</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="76">
         <v>45017</v>
       </c>
@@ -21039,7 +20946,7 @@
         <v>1.0962000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="76">
         <v>45047</v>
       </c>
@@ -21047,7 +20954,7 @@
         <v>1.0867</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="76">
         <v>45078</v>
       </c>
@@ -21055,7 +20962,7 @@
         <v>1.0840000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="76">
         <v>45108</v>
       </c>
@@ -21063,7 +20970,7 @@
         <v>1.1067</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="76">
         <v>45139</v>
       </c>
@@ -21071,7 +20978,7 @@
         <v>1.091</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="76">
         <v>45170</v>
       </c>
@@ -21079,7 +20986,7 @@
         <v>1.0671999999999999</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="76">
         <v>45200</v>
       </c>
@@ -21087,7 +20994,7 @@
         <v>1.0565</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="76">
         <v>45231</v>
       </c>
@@ -21095,7 +21002,7 @@
         <v>1.0819000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="76">
         <v>45261</v>
       </c>
@@ -21103,7 +21010,7 @@
         <v>1.0909</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="76">
         <v>45292</v>
       </c>
@@ -21111,7 +21018,7 @@
         <v>1.0899000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="76">
         <v>45323</v>
       </c>
@@ -21119,7 +21026,7 @@
         <v>1.0792999999999999</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="76">
         <v>45352</v>
       </c>
@@ -21127,7 +21034,7 @@
         <v>1.087</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="76">
         <v>45383</v>
       </c>
@@ -21135,7 +21042,7 @@
         <v>1.0724</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="76">
         <v>45413</v>
       </c>
@@ -21143,7 +21050,7 @@
         <v>1.081</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="76">
         <v>45444</v>
       </c>
@@ -21151,7 +21058,7 @@
         <v>1.0763</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="76">
         <v>45474</v>
       </c>
@@ -21159,7 +21066,7 @@
         <v>1.0847</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="76">
         <v>45505</v>
       </c>
@@ -21176,7 +21083,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06161075-588E-5843-BB7A-EDB11B09427F}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21188,15 +21095,15 @@
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -21210,7 +21117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -21224,12 +21131,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="8" customFormat="1">
+    <row r="3" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -21237,7 +21144,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -21246,7 +21153,7 @@
         <v>2.453282945060923E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -21254,7 +21161,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -21263,12 +21170,12 @@
         <v>0.81870109796004231</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="8" customFormat="1">
+    <row r="8" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="57" t="s">
         <v>15</v>
       </c>
@@ -21286,7 +21193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="57" t="s">
         <v>15</v>
       </c>
@@ -21303,7 +21210,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="105" t="s">
         <v>19</v>
       </c>
@@ -21320,7 +21227,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="105" t="s">
         <v>19</v>
       </c>
@@ -21337,7 +21244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="105" t="s">
         <v>19</v>
       </c>
@@ -21353,7 +21260,7 @@
       </c>
       <c r="E13" s="94"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="105" t="s">
         <v>19</v>
       </c>
@@ -21369,7 +21276,7 @@
       </c>
       <c r="E14" s="94"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="105" t="s">
         <v>22</v>
       </c>
@@ -21386,7 +21293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="105" t="s">
         <v>22</v>
       </c>
@@ -21403,7 +21310,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="105" t="s">
         <v>22</v>
       </c>
@@ -21419,7 +21326,7 @@
       </c>
       <c r="E17" s="94"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="105" t="s">
         <v>22</v>
       </c>
@@ -21435,7 +21342,7 @@
       </c>
       <c r="E18" s="94"/>
     </row>
-    <row r="19" spans="1:5" s="94" customFormat="1" ht="14.45">
+    <row r="19" spans="1:5" s="94" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="94" t="s">
         <v>23</v>
       </c>
@@ -21449,7 +21356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="94" customFormat="1" ht="14.45">
+    <row r="20" spans="1:5" s="94" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="94" t="s">
         <v>25</v>
       </c>
@@ -21463,7 +21370,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="94" customFormat="1" ht="14.45">
+    <row r="21" spans="1:5" s="94" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="94" t="s">
         <v>26</v>
       </c>
@@ -21478,12 +21385,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="8" customFormat="1">
+    <row r="22" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -21500,7 +21407,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -21517,12 +21424,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="8" customFormat="1">
+    <row r="25" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="57" t="s">
         <v>32</v>
       </c>
@@ -21539,7 +21446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="57" t="s">
         <v>32</v>
       </c>
@@ -21556,7 +21463,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="108" customFormat="1" ht="14.45">
+    <row r="29" spans="1:5" s="108" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="108" t="s">
         <v>33</v>
       </c>
@@ -21584,17 +21491,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E1155D-2A55-0744-BB3C-78DAEE3CB015}">
   <dimension ref="A1:AN55"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.125" customWidth="1"/>
-    <col min="2" max="2" width="20.125" customWidth="1"/>
+    <col min="1" max="1" width="23.09765625" customWidth="1"/>
+    <col min="2" max="2" width="20.09765625" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="35" max="35" width="8.625" style="47"/>
-    <col min="36" max="36" width="17.125" style="41" customWidth="1"/>
-    <col min="37" max="37" width="13.625" customWidth="1"/>
+    <col min="35" max="35" width="8.59765625" style="47"/>
+    <col min="36" max="36" width="17.09765625" style="41" customWidth="1"/>
+    <col min="37" max="37" width="13.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" s="31" t="s">
         <v>35</v>
       </c>
@@ -21710,7 +21617,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:38">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>43</v>
       </c>
@@ -21827,7 +21734,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:38">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" s="40" t="s">
         <v>51</v>
       </c>
@@ -21934,7 +21841,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:38">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" s="40" t="s">
         <v>53</v>
       </c>
@@ -22041,7 +21948,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:38">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="40" t="s">
         <v>55</v>
       </c>
@@ -22148,7 +22055,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:38">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="40" t="s">
         <v>56</v>
       </c>
@@ -22255,7 +22162,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:38">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" s="40" t="s">
         <v>57</v>
       </c>
@@ -22362,7 +22269,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:38">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" s="40" t="s">
         <v>58</v>
       </c>
@@ -22469,7 +22376,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:38">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" s="40" t="s">
         <v>59</v>
       </c>
@@ -22576,7 +22483,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:38">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" s="40" t="s">
         <v>60</v>
       </c>
@@ -22683,7 +22590,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:38">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" s="40" t="s">
         <v>61</v>
       </c>
@@ -22790,7 +22697,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:38">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" s="40" t="s">
         <v>62</v>
       </c>
@@ -22897,7 +22804,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:38">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" s="40" t="s">
         <v>63</v>
       </c>
@@ -23004,7 +22911,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:38">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A14" s="34" t="s">
         <v>43</v>
       </c>
@@ -23121,7 +23028,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:38">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" s="40" t="s">
         <v>64</v>
       </c>
@@ -23228,7 +23135,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:38">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16" s="40" t="s">
         <v>65</v>
       </c>
@@ -23335,7 +23242,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:38">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A17" s="40" t="s">
         <v>66</v>
       </c>
@@ -23442,7 +23349,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:38">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A18" s="40" t="s">
         <v>67</v>
       </c>
@@ -23549,7 +23456,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:38">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A19" s="40" t="s">
         <v>68</v>
       </c>
@@ -23666,7 +23573,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:38">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A20" s="40" t="s">
         <v>51</v>
       </c>
@@ -23773,7 +23680,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:38">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A21" s="40" t="s">
         <v>53</v>
       </c>
@@ -23880,7 +23787,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:38">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A22" s="40" t="s">
         <v>55</v>
       </c>
@@ -23987,7 +23894,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:38">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A23" s="40" t="s">
         <v>56</v>
       </c>
@@ -24094,7 +24001,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:38">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A24" s="40" t="s">
         <v>57</v>
       </c>
@@ -24201,7 +24108,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:38">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A25" s="40" t="s">
         <v>58</v>
       </c>
@@ -24308,7 +24215,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:38">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A26" s="40" t="s">
         <v>59</v>
       </c>
@@ -24415,7 +24322,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:38">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A27" s="40" t="s">
         <v>60</v>
       </c>
@@ -24522,7 +24429,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:38">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A28" s="40" t="s">
         <v>61</v>
       </c>
@@ -24629,7 +24536,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:38">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A29" s="40" t="s">
         <v>62</v>
       </c>
@@ -24736,7 +24643,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:38">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A30" s="40" t="s">
         <v>63</v>
       </c>
@@ -24843,7 +24750,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:38" s="2" customFormat="1">
+    <row r="31" spans="1:38" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="34" t="s">
         <v>43</v>
       </c>
@@ -24960,7 +24867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:38">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A32" s="40" t="s">
         <v>64</v>
       </c>
@@ -25067,7 +24974,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:40">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A33" s="40" t="s">
         <v>65</v>
       </c>
@@ -25174,7 +25081,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:40">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A34" s="40" t="s">
         <v>66</v>
       </c>
@@ -25281,7 +25188,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:40">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A35" s="40" t="s">
         <v>67</v>
       </c>
@@ -25388,7 +25295,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:40">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A36" s="40" t="s">
         <v>68</v>
       </c>
@@ -25505,7 +25412,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:40">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A37" s="40" t="s">
         <v>72</v>
       </c>
@@ -25532,7 +25439,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:40">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A38" s="40" t="s">
         <v>72</v>
       </c>
@@ -25556,7 +25463,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:40">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A39" s="40" t="s">
         <v>75</v>
       </c>
@@ -25589,7 +25496,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:40">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A40" s="40" t="s">
         <v>75</v>
       </c>
@@ -25610,14 +25517,14 @@
         <v>1.89E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:40">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>79</v>
       </c>
       <c r="AI42"/>
       <c r="AJ42"/>
     </row>
-    <row r="43" spans="1:40">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A43" s="97"/>
       <c r="B43" s="98" t="s">
         <v>80</v>
@@ -25643,7 +25550,7 @@
       <c r="AI43"/>
       <c r="AJ43"/>
     </row>
-    <row r="44" spans="1:40" s="1" customFormat="1">
+    <row r="44" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="99" t="s">
         <v>87</v>
       </c>
@@ -25672,7 +25579,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:40">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A45" s="97"/>
       <c r="B45" s="100" t="s">
         <v>88</v>
@@ -25701,7 +25608,7 @@
       <c r="AI45"/>
       <c r="AJ45"/>
     </row>
-    <row r="46" spans="1:40">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A46" s="97"/>
       <c r="B46" s="100" t="s">
         <v>88</v>
@@ -25730,7 +25637,7 @@
       <c r="AI46"/>
       <c r="AJ46"/>
     </row>
-    <row r="47" spans="1:40" s="1" customFormat="1">
+    <row r="47" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="99" t="s">
         <v>94</v>
       </c>
@@ -25761,44 +25668,44 @@
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:40">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>98</v>
       </c>
       <c r="AI48"/>
       <c r="AJ48"/>
     </row>
-    <row r="49" spans="1:36">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>99</v>
       </c>
       <c r="AI49"/>
       <c r="AJ49"/>
     </row>
-    <row r="50" spans="1:36">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>100</v>
       </c>
       <c r="AI50"/>
       <c r="AJ50"/>
     </row>
-    <row r="51" spans="1:36">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.3">
       <c r="AI51"/>
       <c r="AJ51"/>
     </row>
-    <row r="52" spans="1:36">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.3">
       <c r="AI52"/>
       <c r="AJ52"/>
     </row>
-    <row r="53" spans="1:36">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.3">
       <c r="AI53"/>
       <c r="AJ53"/>
     </row>
-    <row r="54" spans="1:36">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.3">
       <c r="AI54"/>
       <c r="AJ54"/>
     </row>
-    <row r="55" spans="1:36">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.3">
       <c r="AI55"/>
       <c r="AJ55"/>
     </row>
@@ -25820,17 +25727,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C700A40-351E-EE4C-92AD-3BC93D7F11F0}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AR27"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="10"/>
-    <col min="2" max="2" width="69.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.59765625" style="10"/>
+    <col min="2" max="2" width="69.59765625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="10.625" style="10"/>
+    <col min="6" max="16384" width="10.59765625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -25876,7 +25783,7 @@
       <c r="AQ1" s="9"/>
       <c r="AR1" s="9"/>
     </row>
-    <row r="2" spans="1:44" ht="20.45" thickBot="1">
+    <row r="2" spans="1:44" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9"/>
       <c r="B2" s="11" t="s">
         <v>101</v>
@@ -25924,7 +25831,7 @@
       <c r="AQ2" s="9"/>
       <c r="AR2" s="9"/>
     </row>
-    <row r="3" spans="1:44" ht="16.149999999999999" thickTop="1">
+    <row r="3" spans="1:44" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -25970,7 +25877,7 @@
       <c r="AQ3" s="9"/>
       <c r="AR3" s="9"/>
     </row>
-    <row r="4" spans="1:44">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
         <v>102</v>
@@ -26020,7 +25927,7 @@
       <c r="AQ4" s="9"/>
       <c r="AR4" s="9"/>
     </row>
-    <row r="5" spans="1:44">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="9" t="s">
         <v>6</v>
@@ -26128,7 +26035,7 @@
       <c r="AQ5" s="15"/>
       <c r="AR5" s="15"/>
     </row>
-    <row r="6" spans="1:44">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="16"/>
       <c r="B6" s="16" t="s">
         <v>105</v>
@@ -26234,7 +26141,7 @@
       <c r="AQ6" s="19"/>
       <c r="AR6" s="19"/>
     </row>
-    <row r="7" spans="1:44">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="20"/>
       <c r="B7" s="20" t="s">
         <v>106</v>
@@ -26340,7 +26247,7 @@
       <c r="AQ7" s="24"/>
       <c r="AR7" s="24"/>
     </row>
-    <row r="8" spans="1:44">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="25"/>
@@ -26386,7 +26293,7 @@
       <c r="AQ8" s="25"/>
       <c r="AR8" s="25"/>
     </row>
-    <row r="9" spans="1:44">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="12" t="s">
         <v>107</v>
@@ -26434,7 +26341,7 @@
       <c r="AQ9" s="25"/>
       <c r="AR9" s="25"/>
     </row>
-    <row r="10" spans="1:44">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="12" t="s">
         <v>108</v>
@@ -26482,7 +26389,7 @@
       <c r="AQ10" s="25"/>
       <c r="AR10" s="25"/>
     </row>
-    <row r="11" spans="1:44">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="12" t="s">
         <v>109</v>
@@ -26588,7 +26495,7 @@
       <c r="AQ11" s="25"/>
       <c r="AR11" s="25"/>
     </row>
-    <row r="12" spans="1:44">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="12" t="s">
         <v>110</v>
@@ -26636,7 +26543,7 @@
       <c r="AQ12" s="25"/>
       <c r="AR12" s="25"/>
     </row>
-    <row r="13" spans="1:44">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13" s="12" t="s">
         <v>109</v>
@@ -26742,7 +26649,7 @@
       <c r="AQ13" s="9"/>
       <c r="AR13" s="9"/>
     </row>
-    <row r="14" spans="1:44">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="12" t="s">
         <v>111</v>
@@ -26790,7 +26697,7 @@
       <c r="AQ14" s="9"/>
       <c r="AR14" s="9"/>
     </row>
-    <row r="15" spans="1:44">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15" s="12" t="s">
         <v>109</v>
@@ -26896,7 +26803,7 @@
       <c r="AQ15" s="9"/>
       <c r="AR15" s="9"/>
     </row>
-    <row r="16" spans="1:44">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="25"/>
@@ -26942,7 +26849,7 @@
       <c r="AQ16" s="9"/>
       <c r="AR16" s="9"/>
     </row>
-    <row r="17" spans="1:44">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -26988,7 +26895,7 @@
       <c r="AQ17" s="9"/>
       <c r="AR17" s="9"/>
     </row>
-    <row r="18" spans="1:44" ht="20.45" thickBot="1">
+    <row r="18" spans="1:44" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="9"/>
       <c r="B18" s="11" t="s">
         <v>112</v>
@@ -27036,7 +26943,7 @@
       <c r="AQ18" s="9"/>
       <c r="AR18" s="9"/>
     </row>
-    <row r="19" spans="1:44" ht="16.149999999999999" thickTop="1">
+    <row r="19" spans="1:44" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -27082,7 +26989,7 @@
       <c r="AQ19" s="9"/>
       <c r="AR19" s="9"/>
     </row>
-    <row r="20" spans="1:44">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -27129,7 +27036,7 @@
       <c r="AQ20" s="9"/>
       <c r="AR20" s="9"/>
     </row>
-    <row r="21" spans="1:44">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9" t="s">
         <v>112</v>
@@ -27180,7 +27087,7 @@
       <c r="AQ21" s="9"/>
       <c r="AR21" s="9"/>
     </row>
-    <row r="22" spans="1:44">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -27226,7 +27133,7 @@
       <c r="AQ22" s="9"/>
       <c r="AR22" s="9"/>
     </row>
-    <row r="23" spans="1:44">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -27272,7 +27179,7 @@
       <c r="AQ23" s="9"/>
       <c r="AR23" s="9"/>
     </row>
-    <row r="24" spans="1:44">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
@@ -27314,7 +27221,7 @@
       <c r="AQ24" s="9"/>
       <c r="AR24" s="9"/>
     </row>
-    <row r="25" spans="1:44">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -27360,7 +27267,7 @@
       <c r="AQ25" s="9"/>
       <c r="AR25" s="9"/>
     </row>
-    <row r="26" spans="1:44">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -27406,7 +27313,7 @@
       <c r="AQ26" s="9"/>
       <c r="AR26" s="9"/>
     </row>
-    <row r="27" spans="1:44">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -27460,20 +27367,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6861D5-92D2-D641-8B69-D340B89E733B}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="144" t="s">
         <v>114</v>
       </c>
       <c r="B1" s="144"/>
       <c r="C1" s="144"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -27481,7 +27388,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>406</v>
       </c>
@@ -27489,7 +27396,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>358</v>
       </c>
@@ -27497,7 +27404,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>117</v>
       </c>
@@ -27509,13 +27416,13 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="144" t="s">
         <v>119</v>
       </c>
       <c r="B9" s="144"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>2024</v>
       </c>
@@ -27523,7 +27430,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>120</v>
       </c>
@@ -27537,7 +27444,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>121</v>
       </c>
@@ -27548,13 +27455,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="144" t="s">
         <v>122</v>
       </c>
       <c r="B14" s="144"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>2024</v>
       </c>
@@ -27562,7 +27469,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>120</v>
       </c>
@@ -27573,7 +27480,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -27601,13 +27508,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B5CED7-41F6-FF44-BBF4-DBE0D457C1E0}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A2:C2"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -27626,31 +27533,31 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA419E9D-493B-4DCE-A933-2A9A9AF40246}">
   <dimension ref="A1:AD57"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" outlineLevelCol="2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.125" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="8.875" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="1" max="1" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.09765625" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="8.8984375" hidden="1" customWidth="1" outlineLevel="2"/>
     <col min="4" max="4" width="7" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="5" max="5" width="11.625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="6" max="6" width="16.625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="7" max="8" width="8.875" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="9" max="9" width="10.625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="10" max="10" width="8.375" bestFit="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="5" max="5" width="11.59765625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="6" max="6" width="16.59765625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="7" max="8" width="8.8984375" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="9" max="9" width="10.59765625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="10" max="10" width="8.3984375" bestFit="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="12" max="13" width="8" customWidth="1"/>
-    <col min="14" max="15" width="16.625" customWidth="1"/>
-    <col min="16" max="16" width="20.625" customWidth="1"/>
+    <col min="14" max="15" width="16.59765625" customWidth="1"/>
+    <col min="16" max="16" width="20.59765625" customWidth="1"/>
     <col min="17" max="17" width="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="37.75" customWidth="1"/>
-    <col min="20" max="20" width="34.25" customWidth="1"/>
-    <col min="21" max="21" width="33.875" customWidth="1"/>
-    <col min="22" max="22" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="24" max="30" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.09765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="37.69921875" customWidth="1"/>
+    <col min="20" max="20" width="34.19921875" customWidth="1"/>
+    <col min="21" max="21" width="33.8984375" customWidth="1"/>
+    <col min="22" max="22" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="24" max="30" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
@@ -27734,7 +27641,7 @@
       <c r="AC1" s="82"/>
       <c r="AD1" s="82"/>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -27790,7 +27697,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>150</v>
       </c>
@@ -27846,7 +27753,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>150</v>
       </c>
@@ -27900,7 +27807,7 @@
       </c>
       <c r="W4" s="60"/>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>150</v>
       </c>
@@ -27954,7 +27861,7 @@
       </c>
       <c r="W5" s="60"/>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>150</v>
       </c>
@@ -28008,7 +27915,7 @@
       </c>
       <c r="W6" s="60"/>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>150</v>
       </c>
@@ -28062,7 +27969,7 @@
       </c>
       <c r="W7" s="60"/>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>150</v>
       </c>
@@ -28116,7 +28023,7 @@
       </c>
       <c r="W8" s="60"/>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -28170,7 +28077,7 @@
       </c>
       <c r="W9" s="60"/>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -28224,7 +28131,7 @@
       </c>
       <c r="W10" s="60"/>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -28278,7 +28185,7 @@
       </c>
       <c r="W11" s="60"/>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>150</v>
       </c>
@@ -28332,7 +28239,7 @@
       </c>
       <c r="W12" s="60"/>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>150</v>
       </c>
@@ -28386,7 +28293,7 @@
       </c>
       <c r="W13" s="60"/>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>150</v>
       </c>
@@ -28440,7 +28347,7 @@
       </c>
       <c r="W14" s="60"/>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>150</v>
       </c>
@@ -28494,7 +28401,7 @@
       </c>
       <c r="W15" s="60"/>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>150</v>
       </c>
@@ -28551,7 +28458,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>150</v>
       </c>
@@ -28608,7 +28515,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>150</v>
       </c>
@@ -28650,7 +28557,7 @@
       </c>
       <c r="W18" s="60"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>150</v>
       </c>
@@ -28692,7 +28599,7 @@
       </c>
       <c r="W19" s="60"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>150</v>
       </c>
@@ -28728,7 +28635,7 @@
       </c>
       <c r="W20" s="60"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>150</v>
       </c>
@@ -28764,7 +28671,7 @@
       </c>
       <c r="W21" s="60"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>150</v>
       </c>
@@ -28800,7 +28707,7 @@
       </c>
       <c r="W22" s="60"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>150</v>
       </c>
@@ -28836,7 +28743,7 @@
       </c>
       <c r="W23" s="60"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -28878,7 +28785,7 @@
       </c>
       <c r="W24" s="60"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>150</v>
       </c>
@@ -28929,7 +28836,7 @@
       </c>
       <c r="W25" s="60"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>150</v>
       </c>
@@ -28965,7 +28872,7 @@
       </c>
       <c r="W26" s="60"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>150</v>
       </c>
@@ -29001,7 +28908,7 @@
       </c>
       <c r="W27" s="60"/>
     </row>
-    <row r="28" spans="1:26" s="48" customFormat="1">
+    <row r="28" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="48" t="s">
         <v>150</v>
       </c>
@@ -29031,7 +28938,7 @@
       </c>
       <c r="W28" s="90"/>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>150</v>
       </c>
@@ -29067,7 +28974,7 @@
       </c>
       <c r="W29" s="60"/>
     </row>
-    <row r="30" spans="1:26" s="48" customFormat="1">
+    <row r="30" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="48" t="s">
         <v>260</v>
       </c>
@@ -29100,7 +29007,7 @@
       </c>
       <c r="W30" s="90"/>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>150</v>
       </c>
@@ -29136,7 +29043,7 @@
       </c>
       <c r="W31" s="60"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>150</v>
       </c>
@@ -29172,7 +29079,7 @@
       </c>
       <c r="W32" s="60"/>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>150</v>
       </c>
@@ -29208,7 +29115,7 @@
       </c>
       <c r="W33" s="60"/>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>150</v>
       </c>
@@ -29244,7 +29151,7 @@
       </c>
       <c r="W34" s="60"/>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>150</v>
       </c>
@@ -29295,7 +29202,7 @@
       </c>
       <c r="W35" s="60"/>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>150</v>
       </c>
@@ -29331,7 +29238,7 @@
       </c>
       <c r="W36" s="60"/>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>150</v>
       </c>
@@ -29367,7 +29274,7 @@
       </c>
       <c r="W37" s="60"/>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>150</v>
       </c>
@@ -29403,7 +29310,7 @@
       </c>
       <c r="W38" s="60"/>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>150</v>
       </c>
@@ -29439,7 +29346,7 @@
       </c>
       <c r="W39" s="60"/>
     </row>
-    <row r="40" spans="1:23" s="48" customFormat="1">
+    <row r="40" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="48" t="s">
         <v>150</v>
       </c>
@@ -29466,7 +29373,7 @@
       </c>
       <c r="W40" s="90"/>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>150</v>
       </c>
@@ -29505,7 +29412,7 @@
       </c>
       <c r="W41" s="60"/>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>150</v>
       </c>
@@ -29547,7 +29454,7 @@
       </c>
       <c r="W42" s="60"/>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -29580,7 +29487,7 @@
       </c>
       <c r="W43" s="60"/>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>150</v>
       </c>
@@ -29613,7 +29520,7 @@
       </c>
       <c r="W44" s="60"/>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>150</v>
       </c>
@@ -29646,7 +29553,7 @@
       </c>
       <c r="W45" s="60"/>
     </row>
-    <row r="46" spans="1:23" s="48" customFormat="1">
+    <row r="46" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="48" t="s">
         <v>150</v>
       </c>
@@ -29673,7 +29580,7 @@
       </c>
       <c r="W46" s="90"/>
     </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>260</v>
       </c>
@@ -29707,7 +29614,7 @@
       </c>
       <c r="W47" s="60"/>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>260</v>
       </c>
@@ -29741,7 +29648,7 @@
       </c>
       <c r="W48" s="60"/>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -29789,7 +29696,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>150</v>
       </c>
@@ -29837,7 +29744,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>150</v>
       </c>
@@ -29885,7 +29792,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>150</v>
       </c>
@@ -29933,7 +29840,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>150</v>
       </c>
@@ -29975,7 +29882,7 @@
       </c>
       <c r="W53" s="60"/>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>150</v>
       </c>
@@ -30011,7 +29918,7 @@
       </c>
       <c r="W54" s="60"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>150</v>
       </c>
@@ -30047,7 +29954,7 @@
       </c>
       <c r="W55" s="60"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>150</v>
       </c>
@@ -30083,7 +29990,7 @@
       </c>
       <c r="W56" s="60"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>150</v>
       </c>
@@ -30140,34 +30047,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99968075-C79E-496E-8470-A0201C505FA7}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AL54"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.125" customWidth="1"/>
-    <col min="2" max="2" width="9.125" customWidth="1"/>
+    <col min="1" max="1" width="23.09765625" customWidth="1"/>
+    <col min="2" max="2" width="9.09765625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="18.5" customWidth="1"/>
-    <col min="7" max="7" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.59765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.875" customWidth="1"/>
-    <col min="12" max="12" width="26.75" customWidth="1"/>
+    <col min="11" max="11" width="30.8984375" customWidth="1"/>
+    <col min="12" max="12" width="26.69921875" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="18.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.125" customWidth="1"/>
-    <col min="19" max="22" width="20.125" customWidth="1"/>
+    <col min="18" max="18" width="18.09765625" customWidth="1"/>
+    <col min="19" max="22" width="20.09765625" customWidth="1"/>
     <col min="24" max="25" width="17.5" customWidth="1"/>
-    <col min="26" max="28" width="15.125" customWidth="1"/>
+    <col min="26" max="28" width="15.09765625" customWidth="1"/>
     <col min="29" max="29" width="22.5" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="22.5" customWidth="1"/>
-    <col min="32" max="32" width="37.625" customWidth="1"/>
+    <col min="32" max="32" width="37.59765625" customWidth="1"/>
     <col min="33" max="33" width="19" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="19" customWidth="1"/>
-    <col min="36" max="36" width="33.625" customWidth="1"/>
+    <col min="36" max="36" width="33.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="51" customFormat="1">
+    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -30227,7 +30134,7 @@
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38" s="117" customFormat="1">
+    <row r="2" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="117" t="s">
         <v>151</v>
       </c>
@@ -30258,7 +30165,7 @@
       <c r="R2" s="118"/>
       <c r="AI2" s="119"/>
     </row>
-    <row r="3" spans="1:38" s="117" customFormat="1">
+    <row r="3" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="117" t="s">
         <v>151</v>
       </c>
@@ -30290,7 +30197,7 @@
       <c r="R3" s="118"/>
       <c r="AI3" s="119"/>
     </row>
-    <row r="4" spans="1:38" s="117" customFormat="1">
+    <row r="4" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="117" t="s">
         <v>151</v>
       </c>
@@ -30322,7 +30229,7 @@
       <c r="R4" s="118"/>
       <c r="AI4" s="119"/>
     </row>
-    <row r="5" spans="1:38" s="117" customFormat="1">
+    <row r="5" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="117" t="s">
         <v>151</v>
       </c>
@@ -30355,7 +30262,7 @@
       <c r="AD5" s="120"/>
       <c r="AI5" s="119"/>
     </row>
-    <row r="6" spans="1:38" s="117" customFormat="1">
+    <row r="6" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="117" t="s">
         <v>185</v>
       </c>
@@ -30386,7 +30293,7 @@
       </c>
       <c r="R6" s="121"/>
     </row>
-    <row r="7" spans="1:38" s="117" customFormat="1">
+    <row r="7" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="117" t="s">
         <v>185</v>
       </c>
@@ -30418,7 +30325,7 @@
       <c r="O7" s="122"/>
       <c r="R7" s="121"/>
     </row>
-    <row r="8" spans="1:38" s="117" customFormat="1">
+    <row r="8" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="117" t="s">
         <v>185</v>
       </c>
@@ -30450,7 +30357,7 @@
       <c r="R8" s="121"/>
       <c r="AD8" s="120"/>
     </row>
-    <row r="9" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="9" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>199</v>
       </c>
@@ -30485,7 +30392,7 @@
       <c r="W9" s="114"/>
       <c r="AF9" s="115"/>
     </row>
-    <row r="10" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="10" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>208</v>
       </c>
@@ -30522,7 +30429,7 @@
       <c r="R10" s="113"/>
       <c r="AI10" s="116"/>
     </row>
-    <row r="11" spans="1:38" s="117" customFormat="1">
+    <row r="11" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="117" t="s">
         <v>214</v>
       </c>
@@ -30553,7 +30460,7 @@
       <c r="R11" s="121"/>
       <c r="AI11" s="119"/>
     </row>
-    <row r="12" spans="1:38" s="117" customFormat="1">
+    <row r="12" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="117" t="s">
         <v>214</v>
       </c>
@@ -30584,7 +30491,7 @@
       <c r="R12" s="121"/>
       <c r="AI12" s="119"/>
     </row>
-    <row r="13" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="13" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>223</v>
       </c>
@@ -30619,7 +30526,7 @@
       <c r="AA13" s="124"/>
       <c r="AB13" s="124"/>
     </row>
-    <row r="14" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="14" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>227</v>
       </c>
@@ -30656,7 +30563,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="15" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="15" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>230</v>
       </c>
@@ -30688,7 +30595,7 @@
       <c r="AI15" s="116"/>
       <c r="AL15" s="127"/>
     </row>
-    <row r="16" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="16" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>230</v>
       </c>
@@ -30720,7 +30627,7 @@
       <c r="AI16" s="116"/>
       <c r="AL16" s="127"/>
     </row>
-    <row r="17" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="17" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>234</v>
       </c>
@@ -30751,7 +30658,7 @@
       <c r="R17" s="123"/>
       <c r="AI17" s="116"/>
     </row>
-    <row r="18" spans="1:36" s="128" customFormat="1" hidden="1">
+    <row r="18" spans="1:36" s="128" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="128" t="s">
         <v>240</v>
       </c>
@@ -30779,7 +30686,7 @@
       <c r="R18" s="129"/>
       <c r="W18" s="130"/>
     </row>
-    <row r="19" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="19" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>247</v>
       </c>
@@ -30814,7 +30721,7 @@
       <c r="R19" s="123"/>
       <c r="X19" s="123"/>
     </row>
-    <row r="20" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="20" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>247</v>
       </c>
@@ -30846,7 +30753,7 @@
       <c r="R20" s="123"/>
       <c r="X20" s="123"/>
     </row>
-    <row r="21" spans="1:36" s="127" customFormat="1" hidden="1">
+    <row r="21" spans="1:36" s="127" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="127" t="s">
         <v>251</v>
       </c>
@@ -30865,7 +30772,7 @@
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
     </row>
-    <row r="22" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="22" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>255</v>
       </c>
@@ -30907,7 +30814,7 @@
       <c r="AB22" s="124"/>
       <c r="AF22" s="115"/>
     </row>
-    <row r="23" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="23" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>267</v>
       </c>
@@ -30941,7 +30848,7 @@
       <c r="X23" s="123"/>
       <c r="AI23" s="116"/>
     </row>
-    <row r="24" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="24" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>267</v>
       </c>
@@ -30975,7 +30882,7 @@
       <c r="X24" s="123"/>
       <c r="AI24" s="116"/>
     </row>
-    <row r="25" spans="1:36" s="60" customFormat="1" hidden="1">
+    <row r="25" spans="1:36" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="60" t="s">
         <v>271</v>
       </c>
@@ -30999,7 +30906,7 @@
       </c>
       <c r="AI25" s="93"/>
     </row>
-    <row r="26" spans="1:36" s="117" customFormat="1">
+    <row r="26" spans="1:36" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="117" t="s">
         <v>275</v>
       </c>
@@ -31029,7 +30936,7 @@
       </c>
       <c r="X26" s="138"/>
     </row>
-    <row r="27" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="27" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>278</v>
       </c>
@@ -31063,7 +30970,7 @@
       <c r="R27" s="126"/>
       <c r="X27" s="123"/>
     </row>
-    <row r="28" spans="1:36" hidden="1">
+    <row r="28" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="88" t="s">
         <v>285</v>
       </c>
@@ -31091,7 +30998,7 @@
       <c r="AI28" s="53"/>
       <c r="AJ28" s="48"/>
     </row>
-    <row r="29" spans="1:36" hidden="1">
+    <row r="29" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="88" t="s">
         <v>285</v>
       </c>
@@ -31119,7 +31026,7 @@
       <c r="AI29" s="53"/>
       <c r="AJ29" s="48"/>
     </row>
-    <row r="30" spans="1:36" hidden="1">
+    <row r="30" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="88" t="s">
         <v>285</v>
       </c>
@@ -31147,7 +31054,7 @@
       <c r="AI30" s="53"/>
       <c r="AJ30" s="48"/>
     </row>
-    <row r="31" spans="1:36" ht="25.9" hidden="1" customHeight="1">
+    <row r="31" spans="1:36" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="88" t="s">
         <v>285</v>
       </c>
@@ -31176,7 +31083,7 @@
       <c r="AI31" s="53"/>
       <c r="AJ31" s="48"/>
     </row>
-    <row r="32" spans="1:36" s="48" customFormat="1" hidden="1">
+    <row r="32" spans="1:36" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="48" t="s">
         <v>290</v>
       </c>
@@ -31193,7 +31100,7 @@
       <c r="AH32"/>
       <c r="AI32" s="87"/>
     </row>
-    <row r="33" spans="1:35" s="112" customFormat="1" hidden="1">
+    <row r="33" spans="1:35" s="112" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="112" t="s">
         <v>294</v>
       </c>
@@ -31227,7 +31134,7 @@
       <c r="L33" s="41"/>
       <c r="X33" s="132"/>
     </row>
-    <row r="34" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="34" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>301</v>
       </c>
@@ -31258,7 +31165,7 @@
       <c r="Q34" s="127"/>
       <c r="AI34" s="116"/>
     </row>
-    <row r="35" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="35" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>307</v>
       </c>
@@ -31287,7 +31194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="36" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>311</v>
       </c>
@@ -31319,7 +31226,7 @@
       <c r="X36" s="133"/>
       <c r="AA36" s="134"/>
     </row>
-    <row r="37" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="37" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>315</v>
       </c>
@@ -31346,7 +31253,7 @@
       </c>
       <c r="R37" s="126"/>
     </row>
-    <row r="38" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="38" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="127" t="s">
         <v>319</v>
       </c>
@@ -31362,7 +31269,7 @@
       </c>
       <c r="F38" s="127"/>
     </row>
-    <row r="39" spans="1:35" s="117" customFormat="1">
+    <row r="39" spans="1:35" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="122" t="s">
         <v>329</v>
       </c>
@@ -31394,7 +31301,7 @@
       <c r="R39" s="141"/>
       <c r="X39" s="141"/>
     </row>
-    <row r="40" spans="1:35" s="117" customFormat="1">
+    <row r="40" spans="1:35" s="117" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="122" t="s">
         <v>329</v>
       </c>
@@ -31428,7 +31335,7 @@
       <c r="AE40" s="120"/>
       <c r="AF40" s="142"/>
     </row>
-    <row r="41" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="41" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="124" t="s">
         <v>336</v>
       </c>
@@ -31460,7 +31367,7 @@
       <c r="AD41" s="135"/>
       <c r="AE41" s="43"/>
     </row>
-    <row r="42" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="42" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="124" t="s">
         <v>342</v>
       </c>
@@ -31491,7 +31398,7 @@
       <c r="X42" s="123"/>
       <c r="AE42" s="43"/>
     </row>
-    <row r="43" spans="1:35" s="137" customFormat="1" hidden="1">
+    <row r="43" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="124" t="s">
         <v>345</v>
       </c>
@@ -31539,7 +31446,7 @@
       <c r="AG43" s="2"/>
       <c r="AH43" s="2"/>
     </row>
-    <row r="44" spans="1:35" s="137" customFormat="1" hidden="1">
+    <row r="44" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="124" t="s">
         <v>345</v>
       </c>
@@ -31587,7 +31494,7 @@
       <c r="AG44" s="2"/>
       <c r="AH44" s="2"/>
     </row>
-    <row r="45" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="45" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>348</v>
       </c>
@@ -31615,10 +31522,10 @@
       <c r="R45" s="123"/>
       <c r="X45" s="123"/>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A46" s="48"/>
     </row>
-    <row r="50" spans="2:12">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="143" t="s">
         <v>35</v>
       </c>
@@ -31653,7 +31560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="2:12">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="143" t="s">
         <v>402</v>
       </c>
@@ -31672,7 +31579,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="2:12">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="143"/>
       <c r="C52" s="143" t="s">
         <v>404</v>
@@ -31689,7 +31596,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="2:12">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B53" s="143" t="s">
         <v>405</v>
       </c>
@@ -31708,7 +31615,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="2:12">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B54" s="143"/>
       <c r="C54" s="143" t="s">
         <v>404</v>
@@ -31763,5 +31670,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80800E50-85F1-8745-9372-153DAD5875F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80800E50-85F1-8745-9372-153DAD5875F5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Master Standardisation DACCS_LE.xlsx
+++ b/data/Master Standardisation DACCS_LE.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="6797" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B405949-A78B-4C0D-BDCA-D62C47D81B89}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="973" firstSheet="6" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" tabRatio="973" firstSheet="6" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -7338,9 +7338,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8418090-0B0B-C248-B9C6-3EA8C5996CC0}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7354,33 +7354,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E9E050F-07F8-FE48-85C0-51954A76FC24}">
   <sheetPr codeName="Sheet6" filterMode="1"/>
   <dimension ref="A1:AL47"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.09765625" customWidth="1"/>
-    <col min="2" max="2" width="9.09765625" customWidth="1"/>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="9.125" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="18.5" customWidth="1"/>
-    <col min="7" max="7" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.8984375" customWidth="1"/>
-    <col min="12" max="12" width="26.69921875" customWidth="1"/>
+    <col min="11" max="11" width="6.875" customWidth="1"/>
+    <col min="12" max="12" width="26.75" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="18.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.09765625" customWidth="1"/>
-    <col min="19" max="22" width="20.09765625" customWidth="1"/>
+    <col min="18" max="18" width="18.125" customWidth="1"/>
+    <col min="19" max="22" width="20.125" customWidth="1"/>
     <col min="24" max="25" width="17.5" customWidth="1"/>
-    <col min="26" max="28" width="15.09765625" customWidth="1"/>
+    <col min="26" max="28" width="15.125" customWidth="1"/>
     <col min="29" max="29" width="22.5" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="22.5" customWidth="1"/>
-    <col min="32" max="32" width="37.59765625" customWidth="1"/>
+    <col min="32" max="32" width="37.625" customWidth="1"/>
     <col min="33" max="33" width="19" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="19" customWidth="1"/>
-    <col min="36" max="36" width="33.59765625" customWidth="1"/>
+    <col min="36" max="36" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="AI3" s="53"/>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="AI4" s="53"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="AI5" s="53"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>185</v>
       </c>
@@ -8000,7 +8000,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>185</v>
       </c>
@@ -8099,7 +8099,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>185</v>
       </c>
@@ -8198,7 +8198,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>199</v>
       </c>
@@ -8297,7 +8297,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="10" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>208</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>214</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>214</v>
       </c>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AI12" s="53"/>
     </row>
-    <row r="13" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>223</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>227</v>
       </c>
@@ -8759,7 +8759,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="15" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>230</v>
       </c>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="AL15" s="48"/>
     </row>
-    <row r="16" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>230</v>
       </c>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="AL16" s="48"/>
     </row>
-    <row r="17" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>234</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="18" spans="1:37" s="58" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:37" s="58" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="58" t="s">
         <v>240</v>
       </c>
@@ -9138,7 +9138,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="19" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>247</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="20" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>247</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="21" spans="1:37" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:37" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="48" t="s">
         <v>251</v>
       </c>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="AH21"/>
     </row>
-    <row r="22" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>255</v>
       </c>
@@ -9435,7 +9435,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="23" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>267</v>
       </c>
@@ -9539,7 +9539,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="24" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>267</v>
       </c>
@@ -9643,7 +9643,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="25" spans="1:37" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:37" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60" t="s">
         <v>271</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>275</v>
       </c>
@@ -9761,7 +9761,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="27" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>278</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="28" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="88" t="s">
         <v>285</v>
       </c>
@@ -9938,7 +9938,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="29" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="88" t="s">
         <v>285</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="30" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="88" t="s">
         <v>285</v>
       </c>
@@ -10090,7 +10090,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:37" ht="25.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="88" t="s">
         <v>285</v>
       </c>
@@ -10166,7 +10166,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="32" spans="1:37" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:37" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="48" t="s">
         <v>290</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="33" spans="1:37" s="58" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:37" s="58" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58" t="s">
         <v>294</v>
       </c>
@@ -10279,7 +10279,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="34" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>301</v>
       </c>
@@ -10365,7 +10365,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="35" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>307</v>
       </c>
@@ -10457,7 +10457,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="36" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>311</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="37" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>315</v>
       </c>
@@ -10641,7 +10641,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="38" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="48" t="s">
         <v>319</v>
       </c>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="F38" s="48"/>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>329</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>329</v>
       </c>
@@ -10848,7 +10848,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="41" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="55" t="s">
         <v>336</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="42" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="55" t="s">
         <v>342</v>
       </c>
@@ -11023,7 +11023,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="43" spans="1:37" s="92" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:37" s="92" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="55" t="s">
         <v>345</v>
       </c>
@@ -11111,7 +11111,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="44" spans="1:37" s="92" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:37" s="92" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="55" t="s">
         <v>345</v>
       </c>
@@ -11196,7 +11196,7 @@
       </c>
       <c r="AH44"/>
     </row>
-    <row r="45" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>348</v>
       </c>
@@ -11274,10 +11274,10 @@
         <v>450</v>
       </c>
     </row>
-    <row r="46" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="48"/>
     </row>
-    <row r="47" spans="1:37" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:37" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:AL47" xr:uid="{2E9E050F-07F8-FE48-85C0-51954A76FC24}">
     <filterColumn colId="0">
@@ -11323,25 +11323,25 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:W180"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="40.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.59765625" customWidth="1"/>
-    <col min="6" max="6" width="8.8984375" customWidth="1"/>
-    <col min="7" max="7" width="19.59765625" customWidth="1"/>
+    <col min="4" max="4" width="40.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.625" customWidth="1"/>
+    <col min="6" max="6" width="8.875" customWidth="1"/>
+    <col min="7" max="7" width="19.625" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="15.3984375" customWidth="1"/>
-    <col min="11" max="11" width="13.59765625" customWidth="1"/>
-    <col min="12" max="13" width="24.09765625" customWidth="1"/>
-    <col min="14" max="14" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.09765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="22" width="18.09765625" customWidth="1"/>
+    <col min="10" max="10" width="15.375" customWidth="1"/>
+    <col min="11" max="11" width="13.625" customWidth="1"/>
+    <col min="12" max="13" width="24.125" customWidth="1"/>
+    <col min="14" max="14" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="22" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="L1" s="144" t="s">
         <v>655</v>
       </c>
@@ -11356,7 +11356,7 @@
       <c r="Q1" s="144"/>
       <c r="R1" s="144"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -11427,7 +11427,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -11473,7 +11473,7 @@
         <v>414.8542592918007</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -11518,7 +11518,7 @@
         <v>342.50358359189738</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -11563,7 +11563,7 @@
         <v>523.95174204407829</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>151</v>
       </c>
@@ -11606,7 +11606,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -11649,7 +11649,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>151</v>
       </c>
@@ -11692,7 +11692,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>'Study Parameters'!A3</f>
         <v>Young et al. 2023</v>
@@ -11743,7 +11743,7 @@
         <v>2060.169523488109</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -11788,7 +11788,7 @@
         <v>1488.7216799143798</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>151</v>
       </c>
@@ -11833,7 +11833,7 @@
         <v>2729.5646158724885</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>151</v>
       </c>
@@ -11877,7 +11877,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>151</v>
       </c>
@@ -11921,7 +11921,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>151</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>'Study Parameters'!A4</f>
         <v>Young et al. 2023</v>
@@ -12015,7 +12015,7 @@
         <v>1308.9151041939408</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>151</v>
       </c>
@@ -12059,7 +12059,7 @@
         <v>1185.9075603382862</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>151</v>
       </c>
@@ -12103,7 +12103,7 @@
         <v>1518.5576325147504</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>151</v>
       </c>
@@ -12146,7 +12146,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>151</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -12232,7 +12232,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>'Study Parameters'!A5</f>
         <v>Young et al. 2023</v>
@@ -12282,7 +12282,7 @@
         <v>484.59306078439545</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>151</v>
       </c>
@@ -12326,7 +12326,7 @@
         <v>382.81191676230259</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>151</v>
       </c>
@@ -12370,7 +12370,7 @@
         <v>657.89384726964306</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>151</v>
       </c>
@@ -12413,7 +12413,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>151</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>151</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="48" t="str">
         <f>'Study Parameters'!A6</f>
         <v>Sievert et al. 2024</v>
@@ -12548,7 +12548,7 @@
         <v>669.94069463308699</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>185</v>
       </c>
@@ -12592,7 +12592,7 @@
         <v>521.31303134173265</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>185</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>894.39776183919753</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>185</v>
       </c>
@@ -12679,7 +12679,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>185</v>
       </c>
@@ -12722,7 +12722,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>185</v>
       </c>
@@ -12765,7 +12765,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>'Study Parameters'!A7</f>
         <v>Sievert et al. 2024</v>
@@ -12814,7 +12814,7 @@
         <v>1282.314450530346</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>185</v>
       </c>
@@ -12857,7 +12857,7 @@
         <v>1180.094323057237</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>185</v>
       </c>
@@ -12900,7 +12900,7 @@
         <v>1392.3242644152151</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -12943,7 +12943,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>185</v>
       </c>
@@ -12986,7 +12986,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>185</v>
       </c>
@@ -13030,7 +13030,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>'Study Parameters'!A8</f>
         <v>Sievert et al. 2024</v>
@@ -13079,7 +13079,7 @@
         <v>2481.3480043001368</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>185</v>
       </c>
@@ -13122,7 +13122,7 @@
         <v>2153.1601565847341</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>185</v>
       </c>
@@ -13165,7 +13165,7 @@
         <v>2874.3199941446942</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>185</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>185</v>
       </c>
@@ -13253,7 +13253,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>185</v>
       </c>
@@ -13297,7 +13297,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13350,7 +13350,7 @@
         <v>293.01246179996224</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13405,7 +13405,7 @@
         <v>267.3339028754757</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13460,7 +13460,7 @@
         <v>303.19697040786667</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13507,7 +13507,7 @@
         <v>278.51244114406211</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13554,7 +13554,7 @@
         <v>260.17305813012763</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13601,7 +13601,7 @@
         <v>334.02175471233329</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13648,7 +13648,7 @@
         <v>347.52430793993972</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13695,7 +13695,7 @@
         <v>431.20952014305874</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13742,7 +13742,7 @@
         <v>405.58125796275607</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13789,7 +13789,7 @@
         <v>532.88151930075014</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13840,7 +13840,7 @@
         <v>598.00725415939087</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13886,7 +13886,7 @@
         <v>594.26871158968584</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13932,7 +13932,7 @@
         <v>556.61504560775791</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13978,7 +13978,7 @@
         <v>745.92213758183834</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -14024,7 +14024,7 @@
         <v>863.3220713069054</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f>'Study Parameters'!A11</f>
         <v>Fasihi et al. 2019</v>
@@ -14081,7 +14081,7 @@
         <v>289.21430381427916</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>214</v>
       </c>
@@ -14132,7 +14132,7 @@
         <v>289.21430381427916</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>214</v>
       </c>
@@ -14182,7 +14182,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>214</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f>'Study Parameters'!A12</f>
         <v>Fasihi et al. 2019</v>
@@ -14288,7 +14288,7 @@
         <v>292.47958561757542</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>214</v>
       </c>
@@ -14339,7 +14339,7 @@
         <v>292.47958561757542</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>214</v>
       </c>
@@ -14389,7 +14389,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>214</v>
       </c>
@@ -14439,7 +14439,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f>'Study Parameters'!A13</f>
         <v>Mazzotti et al. 2013</v>
@@ -14485,7 +14485,7 @@
       </c>
       <c r="M68" s="30"/>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>223</v>
       </c>
@@ -14525,7 +14525,7 @@
       </c>
       <c r="M69" s="30"/>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>223</v>
       </c>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="M70" s="30"/>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f>'Study Parameters'!A14</f>
         <v>Zeman 2014</v>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="M71" s="30"/>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f>'Study Parameters'!A15</f>
         <v>Prats-Salvado et al. 2024</v>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="M72" s="30"/>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>230</v>
       </c>
@@ -14700,7 +14700,7 @@
       </c>
       <c r="M73" s="30"/>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f>'Study Parameters'!A16</f>
         <v>Prats-Salvado et al. 2024</v>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="M74" s="30"/>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>230</v>
       </c>
@@ -14787,7 +14787,7 @@
       </c>
       <c r="M75" s="30"/>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f>'Study Parameters'!A17</f>
         <v>Terlouw et al. 2024</v>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="M76" s="62"/>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>234</v>
       </c>
@@ -14873,7 +14873,7 @@
       </c>
       <c r="M77" s="62"/>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f>'Study Parameters'!A18</f>
         <v>McQueen et al. 2021</v>
@@ -14917,7 +14917,7 @@
         <v>400.60217261536002</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>240</v>
       </c>
@@ -14956,7 +14956,7 @@
         <v>881.5737078159442</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>240</v>
       </c>
@@ -14995,7 +14995,7 @@
         <v>400.60217261536002</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>240</v>
       </c>
@@ -15034,7 +15034,7 @@
         <v>881.5737078159442</v>
       </c>
     </row>
-    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>240</v>
       </c>
@@ -15073,7 +15073,7 @@
         <v>463.06098024892566</v>
       </c>
     </row>
-    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>240</v>
       </c>
@@ -15112,7 +15112,7 @@
         <v>558.57147419213493</v>
       </c>
     </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>240</v>
       </c>
@@ -15151,7 +15151,7 @@
         <v>777.69611217374995</v>
       </c>
     </row>
-    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>240</v>
       </c>
@@ -15190,7 +15190,7 @@
         <v>2052.1001665091567</v>
       </c>
     </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
         <f>'Study Parameters'!A19</f>
         <v>Datta et al. 2023</v>
@@ -15238,7 +15238,7 @@
       </c>
       <c r="M86" s="30"/>
     </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="str">
         <f>'Study Parameters'!A20</f>
         <v>Datta et al. 2023</v>
@@ -15286,7 +15286,7 @@
       </c>
       <c r="M87" s="30"/>
     </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>255</v>
       </c>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="M88" s="30"/>
     </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>255</v>
       </c>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="M89" s="30"/>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>255</v>
       </c>
@@ -15406,7 +15406,7 @@
       </c>
       <c r="M90" s="30"/>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>255</v>
       </c>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="M91" s="30"/>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>255</v>
       </c>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="M92" s="30"/>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>255</v>
       </c>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="M93" s="30"/>
     </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="M94" s="30"/>
     </row>
-    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>255</v>
       </c>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="M95" s="30"/>
     </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>255</v>
       </c>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="M96" s="30"/>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="str">
         <f>'Study Parameters'!A22</f>
         <v>Simon et al. 2011</v>
@@ -15690,7 +15690,7 @@
         <v>304.707654655694</v>
       </c>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>255</v>
       </c>
@@ -15730,7 +15730,7 @@
         <v>803.14143939193252</v>
       </c>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>255</v>
       </c>
@@ -15770,7 +15770,7 @@
         <v>329.15418006599049</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>267</v>
       </c>
@@ -15808,7 +15808,7 @@
         <v>779.02843503778104</v>
       </c>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>267</v>
       </c>
@@ -15846,7 +15846,7 @@
         <v>831.75510668257198</v>
       </c>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>267</v>
       </c>
@@ -15884,7 +15884,7 @@
         <v>317.24671499539198</v>
       </c>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>267</v>
       </c>
@@ -15922,7 +15922,7 @@
         <v>371.938416568371</v>
       </c>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>267</v>
       </c>
@@ -15960,7 +15960,7 @@
         <v>291.241690193887</v>
       </c>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>267</v>
       </c>
@@ -15998,7 +15998,7 @@
         <v>355.05876736764702</v>
       </c>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>267</v>
       </c>
@@ -16036,7 +16036,7 @@
         <v>267.11083137986202</v>
       </c>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="str">
         <f>'Study Parameters'!A23</f>
         <v>Küng et al. 2023</v>
@@ -16080,7 +16080,7 @@
         <v>314.61251708631102</v>
       </c>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>267</v>
       </c>
@@ -16118,7 +16118,7 @@
         <v>1817.71250053524</v>
       </c>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>267</v>
       </c>
@@ -16156,7 +16156,7 @@
         <v>1990.0315112179401</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>267</v>
       </c>
@@ -16194,7 +16194,7 @@
         <v>980.75097520117902</v>
       </c>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>267</v>
       </c>
@@ -16232,7 +16232,7 @@
         <v>1064.51188379418</v>
       </c>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>267</v>
       </c>
@@ -16270,7 +16270,7 @@
         <v>411.65027432423102</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>267</v>
       </c>
@@ -16308,7 +16308,7 @@
         <v>488.64611354083598</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>267</v>
       </c>
@@ -16346,7 +16346,7 @@
         <v>378.55341271061599</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>267</v>
       </c>
@@ -16384,7 +16384,7 @@
         <v>468.39609948070898</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>267</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>349.10367628750998</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>267</v>
       </c>
@@ -16460,7 +16460,7 @@
         <v>415.97729787873197</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>267</v>
       </c>
@@ -16498,7 +16498,7 @@
         <v>2476.9733161530498</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>267</v>
       </c>
@@ -16536,7 +16536,7 @@
         <v>2750.7170677000299</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="str">
         <f>'Study Parameters'!A24</f>
         <v>Küng et al. 2023</v>
@@ -16579,7 +16579,7 @@
         <v>183.15040372394199</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>267</v>
       </c>
@@ -16617,7 +16617,7 @@
         <v>227.07677281852301</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>267</v>
       </c>
@@ -16655,7 +16655,7 @@
         <v>61.893630816227301</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>267</v>
       </c>
@@ -16693,7 +16693,7 @@
         <v>72.225103599114604</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>267</v>
       </c>
@@ -16731,7 +16731,7 @@
         <v>393.65606020680502</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -16769,7 +16769,7 @@
         <v>503.939346853232</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>267</v>
       </c>
@@ -16807,7 +16807,7 @@
         <v>406.913082895564</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>267</v>
       </c>
@@ -16845,7 +16845,7 @@
         <v>517.19636954199098</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>267</v>
       </c>
@@ -16883,7 +16883,7 @@
         <v>243.248532930187</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>267</v>
       </c>
@@ -16921,7 +16921,7 @@
         <v>305.088767461244</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>267</v>
       </c>
@@ -16959,7 +16959,7 @@
         <v>76.028698179975393</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>267</v>
       </c>
@@ -16997,7 +16997,7 @@
         <v>90.573508350133693</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>267</v>
       </c>
@@ -17035,7 +17035,7 @@
         <v>523.47869237559496</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>267</v>
       </c>
@@ -17073,7 +17073,7 @@
         <v>698.67329510641696</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -17111,7 +17111,7 @@
         <v>536.73571506435496</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>267</v>
       </c>
@@ -17149,7 +17149,7 @@
         <v>711.93031779517605</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="str">
         <f>'Study Parameters'!A25</f>
         <v>Mostafa et al. 2022</v>
@@ -17175,7 +17175,7 @@
       </c>
       <c r="L136" s="30"/>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="str">
         <f>'Study Parameters'!A26</f>
         <v>Keith et al. 2018</v>
@@ -17232,7 +17232,7 @@
         <v>295.67151321600323</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -17280,7 +17280,7 @@
         <v>238.63022727495593</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>275</v>
       </c>
@@ -17328,7 +17328,7 @@
         <v>224.78482396902055</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>275</v>
       </c>
@@ -17375,7 +17375,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>275</v>
       </c>
@@ -17426,7 +17426,7 @@
         <v>295.67151321600323</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>275</v>
       </c>
@@ -17477,7 +17477,7 @@
         <v>238.63022727495593</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>275</v>
       </c>
@@ -17528,7 +17528,7 @@
         <v>224.78482396902055</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>275</v>
       </c>
@@ -17575,7 +17575,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="str">
         <f>'Study Parameters'!A27</f>
         <v>Gray et al. 2024</v>
@@ -17629,7 +17629,7 @@
         <v>1422.4526421724208</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="str">
         <f>'Study Parameters'!A28</f>
         <v>Rosen et al. 2024</v>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="L146" s="30"/>
     </row>
-    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="str">
         <f>'Study Parameters'!A29</f>
         <v>Rosen et al. 2024</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="L147" s="30"/>
     </row>
-    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="str">
         <f>'Study Parameters'!A30</f>
         <v>Rosen et al. 2024</v>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="L148" s="30"/>
     </row>
-    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="str">
         <f>'Study Parameters'!A31</f>
         <v>Rosen et al. 2024</v>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="L149" s="30"/>
     </row>
-    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="str">
         <f>'Study Parameters'!A32</f>
         <v>Sabatino et al. 2020</v>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="L150" s="30"/>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="str">
         <f>'Study Parameters'!A33</f>
         <v>McQueen et al. 2020c</v>
@@ -17830,7 +17830,7 @@
         <v>52.859259278213045</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="str">
         <f>'Study Parameters'!A33</f>
         <v>McQueen et al. 2020c</v>
@@ -17871,7 +17871,7 @@
         <v>174.22096158203897</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>294</v>
       </c>
@@ -17907,7 +17907,7 @@
         <v>45.162595126533958</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>294</v>
       </c>
@@ -17943,7 +17943,7 @@
         <v>155.30185025856494</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="str">
         <f>'Study Parameters'!A34</f>
         <v>Lee et al. 2023</v>
@@ -18001,7 +18001,7 @@
         <v>270.09276004403995</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="str">
         <f>'Study Parameters'!A35</f>
         <v>Abanades et al. 2023</v>
@@ -18028,7 +18028,7 @@
       </c>
       <c r="L156" s="30"/>
     </row>
-    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="str">
         <f>'Study Parameters'!A36</f>
         <v>Abanades et al. 2020</v>
@@ -18055,7 +18055,7 @@
       </c>
       <c r="L157" s="30"/>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="str">
         <f>'Study Parameters'!A37</f>
         <v>Ragipani et al. 2022</v>
@@ -18097,7 +18097,7 @@
         <v>121.14570202833102</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>315</v>
       </c>
@@ -18133,7 +18133,7 @@
         <v>140.09669470231475</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>329</v>
       </c>
@@ -18181,7 +18181,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>329</v>
       </c>
@@ -18229,7 +18229,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>329</v>
       </c>
@@ -18277,7 +18277,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" t="str">
         <f>'Study Parameters'!A39</f>
         <v>Pett-Ridge et al. 2024</v>
@@ -18328,7 +18328,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>329</v>
       </c>
@@ -18375,7 +18375,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>329</v>
       </c>
@@ -18422,7 +18422,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="str">
         <f>'Study Parameters'!A40</f>
         <v>Pett-Ridge et al. 2024</v>
@@ -18475,7 +18475,7 @@
         <v>440.01216847304312</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>329</v>
       </c>
@@ -18523,7 +18523,7 @@
         <v>339.04143355290654</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>329</v>
       </c>
@@ -18571,7 +18571,7 @@
         <v>263.41019772115243</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>329</v>
       </c>
@@ -18615,7 +18615,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="str">
         <f>'Study Parameters'!A41</f>
         <v>NETL/Valentine 2022a</v>
@@ -18661,7 +18661,7 @@
       </c>
       <c r="M170" s="30"/>
     </row>
-    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>336</v>
       </c>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="M171" s="30"/>
     </row>
-    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>336</v>
       </c>
@@ -18741,7 +18741,7 @@
       </c>
       <c r="M172" s="30"/>
     </row>
-    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="str">
         <f>'Study Parameters'!A42</f>
         <v>NETL/Valentine 2022b</v>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="M173" s="30"/>
     </row>
-    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>342</v>
       </c>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="M174" s="30"/>
     </row>
-    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>342</v>
       </c>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="M175" s="30"/>
     </row>
-    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="str">
         <f>'Study Parameters'!A43</f>
         <v>NASEM 2019</v>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="L176" s="30"/>
     </row>
-    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="L177" s="30"/>
     </row>
-    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="L178" s="30"/>
     </row>
-    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="str">
         <f>'Study Parameters'!A45</f>
         <v>APS 2011</v>
@@ -18994,7 +18994,7 @@
       </c>
       <c r="M179" s="30"/>
     </row>
-    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>348</v>
       </c>
@@ -19056,14 +19056,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08C0257C-D407-4235-8443-42A5A3A9A73A}">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.125" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="63" t="s">
         <v>751</v>
       </c>
@@ -19073,7 +19073,7 @@
       <c r="J1" s="74"/>
       <c r="K1" s="74"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
         <v>753</v>
       </c>
@@ -19083,7 +19083,7 @@
       <c r="J2" s="74"/>
       <c r="K2" s="74"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="64"/>
       <c r="F3" s="74" t="s">
         <v>755</v>
@@ -19091,7 +19091,7 @@
       <c r="J3" s="74"/>
       <c r="K3" s="74"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>756</v>
       </c>
@@ -19107,7 +19107,7 @@
       <c r="J4" s="74"/>
       <c r="K4" s="74"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>760</v>
       </c>
@@ -19123,7 +19123,7 @@
       <c r="J5" s="74"/>
       <c r="K5" s="74"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>764</v>
       </c>
@@ -19136,7 +19136,7 @@
       <c r="J6" s="74"/>
       <c r="K6" s="74"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>766</v>
       </c>
@@ -19146,7 +19146,7 @@
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>767</v>
       </c>
@@ -19156,7 +19156,7 @@
       <c r="J8" s="74"/>
       <c r="K8" s="74"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>768</v>
       </c>
@@ -19166,7 +19166,7 @@
       <c r="J9" s="74"/>
       <c r="K9" s="74"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>769</v>
       </c>
@@ -19176,7 +19176,7 @@
       <c r="J10" s="74"/>
       <c r="K10" s="74"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>770</v>
       </c>
@@ -19186,7 +19186,7 @@
       <c r="J11" s="74"/>
       <c r="K11" s="74"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>771</v>
       </c>
@@ -19196,7 +19196,7 @@
       <c r="J12" s="76"/>
       <c r="K12" s="77"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>772</v>
       </c>
@@ -19206,7 +19206,7 @@
       <c r="J13" s="76"/>
       <c r="K13" s="75"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>773</v>
       </c>
@@ -19216,7 +19216,7 @@
       <c r="J14" s="76"/>
       <c r="K14" s="77"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>774</v>
       </c>
@@ -19226,7 +19226,7 @@
       <c r="J15" s="76"/>
       <c r="K15" s="77"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>775</v>
       </c>
@@ -19236,7 +19236,7 @@
       <c r="J16" s="76"/>
       <c r="K16" s="77"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>776</v>
       </c>
@@ -19246,7 +19246,7 @@
       <c r="J17" s="76"/>
       <c r="K17" s="77"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>777</v>
       </c>
@@ -19256,7 +19256,7 @@
       <c r="J18" s="76"/>
       <c r="K18" s="77"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>778</v>
       </c>
@@ -19266,7 +19266,7 @@
       <c r="J19" s="76"/>
       <c r="K19" s="74"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>779</v>
       </c>
@@ -19276,7 +19276,7 @@
       <c r="J20" s="76"/>
       <c r="K20" s="77"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>780</v>
       </c>
@@ -19286,7 +19286,7 @@
       <c r="J21" s="76"/>
       <c r="K21" s="77"/>
     </row>
-    <row r="22" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>96</v>
       </c>
@@ -19297,7 +19297,7 @@
       <c r="J22" s="76"/>
       <c r="K22" s="77"/>
     </row>
-    <row r="23" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="85" t="s">
         <v>80</v>
       </c>
@@ -19328,7 +19328,7 @@
       <c r="J23" s="76"/>
       <c r="K23" s="77"/>
     </row>
-    <row r="24" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="78" t="s">
         <v>782</v>
       </c>
@@ -19359,14 +19359,14 @@
       <c r="J24" s="76"/>
       <c r="K24" s="77"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="86" t="s">
         <v>784</v>
       </c>
       <c r="J25" s="76"/>
       <c r="K25" s="77"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>785</v>
       </c>
@@ -19380,7 +19380,7 @@
       <c r="J26" s="76"/>
       <c r="K26" s="77"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -19403,52 +19403,52 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56965C59-6106-408A-A712-D0B6552D4011}">
   <dimension ref="A1:B211"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="74" t="s">
         <v>752</v>
       </c>
       <c r="B1" s="74"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
         <v>754</v>
       </c>
       <c r="B2" s="74"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="74" t="s">
         <v>755</v>
       </c>
       <c r="B3" s="74"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
         <v>759</v>
       </c>
       <c r="B4" s="74"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="74" t="s">
         <v>763</v>
       </c>
       <c r="B5" s="74"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="74" t="s">
         <v>765</v>
       </c>
       <c r="B6" s="74"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="74"/>
       <c r="B7" s="74"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="74" t="s">
         <v>788</v>
       </c>
@@ -19456,17 +19456,17 @@
         <v>789</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="74"/>
       <c r="B9" s="74"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="74" t="s">
         <v>790</v>
       </c>
       <c r="B10" s="74"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="s">
         <v>791</v>
       </c>
@@ -19474,7 +19474,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="76">
         <v>39448</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>1.4728000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="76">
         <v>39479</v>
       </c>
@@ -19490,7 +19490,7 @@
         <v>1.4759</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="76">
         <v>39508</v>
       </c>
@@ -19498,7 +19498,7 @@
         <v>1.552</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="76">
         <v>39539</v>
       </c>
@@ -19506,7 +19506,7 @@
         <v>1.5753999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="76">
         <v>39569</v>
       </c>
@@ -19514,7 +19514,7 @@
         <v>1.5553999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="76">
         <v>39600</v>
       </c>
@@ -19522,7 +19522,7 @@
         <v>1.5562</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="76">
         <v>39630</v>
       </c>
@@ -19530,7 +19530,7 @@
         <v>1.5759000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="76">
         <v>39661</v>
       </c>
@@ -19538,7 +19538,7 @@
         <v>1.4955000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="76">
         <v>39692</v>
       </c>
@@ -19546,7 +19546,7 @@
         <v>1.4341999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="76">
         <v>39722</v>
       </c>
@@ -19554,7 +19554,7 @@
         <v>1.3266</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="76">
         <v>39753</v>
       </c>
@@ -19562,7 +19562,7 @@
         <v>1.2744</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="76">
         <v>39783</v>
       </c>
@@ -19570,7 +19570,7 @@
         <v>1.3511</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="76">
         <v>39814</v>
       </c>
@@ -19578,7 +19578,7 @@
         <v>1.3244</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="76">
         <v>39845</v>
       </c>
@@ -19586,7 +19586,7 @@
         <v>1.2797000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="76">
         <v>39873</v>
       </c>
@@ -19594,7 +19594,7 @@
         <v>1.3049999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="76">
         <v>39904</v>
       </c>
@@ -19602,7 +19602,7 @@
         <v>1.3199000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="76">
         <v>39934</v>
       </c>
@@ -19610,7 +19610,7 @@
         <v>1.3646</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="76">
         <v>39965</v>
       </c>
@@ -19618,7 +19618,7 @@
         <v>1.4014</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="76">
         <v>39995</v>
       </c>
@@ -19626,7 +19626,7 @@
         <v>1.4092</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="76">
         <v>40026</v>
       </c>
@@ -19634,7 +19634,7 @@
         <v>1.4266000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="76">
         <v>40057</v>
       </c>
@@ -19642,7 +19642,7 @@
         <v>1.4575</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="76">
         <v>40087</v>
       </c>
@@ -19650,7 +19650,7 @@
         <v>1.4821</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="76">
         <v>40118</v>
       </c>
@@ -19658,7 +19658,7 @@
         <v>1.4907999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="76">
         <v>40148</v>
       </c>
@@ -19666,7 +19666,7 @@
         <v>1.4579</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="76">
         <v>40179</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>1.4266000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="76">
         <v>40210</v>
       </c>
@@ -19682,7 +19682,7 @@
         <v>1.3680000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="76">
         <v>40238</v>
       </c>
@@ -19690,7 +19690,7 @@
         <v>1.357</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="76">
         <v>40269</v>
       </c>
@@ -19698,7 +19698,7 @@
         <v>1.3416999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="76">
         <v>40299</v>
       </c>
@@ -19706,7 +19706,7 @@
         <v>1.2563</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="76">
         <v>40330</v>
       </c>
@@ -19714,7 +19714,7 @@
         <v>1.2222999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="76">
         <v>40360</v>
       </c>
@@ -19722,7 +19722,7 @@
         <v>1.2810999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="76">
         <v>40391</v>
       </c>
@@ -19730,7 +19730,7 @@
         <v>1.2903</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="76">
         <v>40422</v>
       </c>
@@ -19738,7 +19738,7 @@
         <v>1.3103</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="76">
         <v>40452</v>
       </c>
@@ -19746,7 +19746,7 @@
         <v>1.3900999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="76">
         <v>40483</v>
       </c>
@@ -19754,7 +19754,7 @@
         <v>1.3653999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="76">
         <v>40513</v>
       </c>
@@ -19762,7 +19762,7 @@
         <v>1.3221000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="76">
         <v>40544</v>
       </c>
@@ -19770,7 +19770,7 @@
         <v>1.3371</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="76">
         <v>40575</v>
       </c>
@@ -19778,7 +19778,7 @@
         <v>1.3655999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="76">
         <v>40603</v>
       </c>
@@ -19786,7 +19786,7 @@
         <v>1.4019999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="76">
         <v>40634</v>
       </c>
@@ -19794,7 +19794,7 @@
         <v>1.446</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="76">
         <v>40664</v>
       </c>
@@ -19802,7 +19802,7 @@
         <v>1.4335</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="76">
         <v>40695</v>
       </c>
@@ -19810,7 +19810,7 @@
         <v>1.4402999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="76">
         <v>40725</v>
       </c>
@@ -19818,7 +19818,7 @@
         <v>1.4275</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="76">
         <v>40756</v>
       </c>
@@ -19826,7 +19826,7 @@
         <v>1.4333</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="76">
         <v>40787</v>
       </c>
@@ -19834,7 +19834,7 @@
         <v>1.3747</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="76">
         <v>40817</v>
       </c>
@@ -19842,7 +19842,7 @@
         <v>1.3732</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="76">
         <v>40848</v>
       </c>
@@ -19850,7 +19850,7 @@
         <v>1.3557999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="76">
         <v>40878</v>
       </c>
@@ -19858,7 +19858,7 @@
         <v>1.3154999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="76">
         <v>40909</v>
       </c>
@@ -19866,7 +19866,7 @@
         <v>1.2909999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="76">
         <v>40940</v>
       </c>
@@ -19874,7 +19874,7 @@
         <v>1.3238000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="76">
         <v>40969</v>
       </c>
@@ -19882,7 +19882,7 @@
         <v>1.3208</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="76">
         <v>41000</v>
       </c>
@@ -19890,7 +19890,7 @@
         <v>1.3160000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="76">
         <v>41030</v>
       </c>
@@ -19898,7 +19898,7 @@
         <v>1.2806</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="76">
         <v>41061</v>
       </c>
@@ -19906,7 +19906,7 @@
         <v>1.2541</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="76">
         <v>41091</v>
       </c>
@@ -19914,7 +19914,7 @@
         <v>1.2278</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="76">
         <v>41122</v>
       </c>
@@ -19922,7 +19922,7 @@
         <v>1.2405999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="76">
         <v>41153</v>
       </c>
@@ -19930,7 +19930,7 @@
         <v>1.2885</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="76">
         <v>41183</v>
       </c>
@@ -19938,7 +19938,7 @@
         <v>1.2974000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="76">
         <v>41214</v>
       </c>
@@ -19946,7 +19946,7 @@
         <v>1.2837000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="76">
         <v>41244</v>
       </c>
@@ -19954,7 +19954,7 @@
         <v>1.3119000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="76">
         <v>41275</v>
       </c>
@@ -19962,7 +19962,7 @@
         <v>1.3304</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="76">
         <v>41306</v>
       </c>
@@ -19970,7 +19970,7 @@
         <v>1.3347</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="76">
         <v>41334</v>
       </c>
@@ -19978,7 +19978,7 @@
         <v>1.2952999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="76">
         <v>41365</v>
       </c>
@@ -19986,7 +19986,7 @@
         <v>1.3025</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="76">
         <v>41395</v>
       </c>
@@ -19994,7 +19994,7 @@
         <v>1.2983</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="76">
         <v>41426</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>1.3197000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="76">
         <v>41456</v>
       </c>
@@ -20010,7 +20010,7 @@
         <v>1.3088</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="76">
         <v>41487</v>
       </c>
@@ -20018,7 +20018,7 @@
         <v>1.3313999999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="76">
         <v>41518</v>
       </c>
@@ -20026,7 +20026,7 @@
         <v>1.3364</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="76">
         <v>41548</v>
       </c>
@@ -20034,7 +20034,7 @@
         <v>1.3646</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="76">
         <v>41579</v>
       </c>
@@ -20042,7 +20042,7 @@
         <v>1.3491</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="76">
         <v>41609</v>
       </c>
@@ -20050,7 +20050,7 @@
         <v>1.3708</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="76">
         <v>41640</v>
       </c>
@@ -20058,7 +20058,7 @@
         <v>1.3617999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="76">
         <v>41671</v>
       </c>
@@ -20066,7 +20066,7 @@
         <v>1.3665</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="76">
         <v>41699</v>
       </c>
@@ -20074,7 +20074,7 @@
         <v>1.3828</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="76">
         <v>41730</v>
       </c>
@@ -20082,7 +20082,7 @@
         <v>1.381</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="76">
         <v>41760</v>
       </c>
@@ -20090,7 +20090,7 @@
         <v>1.3738999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="76">
         <v>41791</v>
       </c>
@@ -20098,7 +20098,7 @@
         <v>1.3594999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="76">
         <v>41821</v>
       </c>
@@ -20106,7 +20106,7 @@
         <v>1.3532999999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="76">
         <v>41852</v>
       </c>
@@ -20114,7 +20114,7 @@
         <v>1.3314999999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="76">
         <v>41883</v>
       </c>
@@ -20122,7 +20122,7 @@
         <v>1.2888999999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="76">
         <v>41913</v>
       </c>
@@ -20130,7 +20130,7 @@
         <v>1.2677</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="76">
         <v>41944</v>
       </c>
@@ -20138,7 +20138,7 @@
         <v>1.2473000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="76">
         <v>41974</v>
       </c>
@@ -20146,7 +20146,7 @@
         <v>1.2329000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="76">
         <v>42005</v>
       </c>
@@ -20154,7 +20154,7 @@
         <v>1.1615</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="76">
         <v>42036</v>
       </c>
@@ -20162,7 +20162,7 @@
         <v>1.135</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="76">
         <v>42064</v>
       </c>
@@ -20170,7 +20170,7 @@
         <v>1.0819000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="76">
         <v>42095</v>
       </c>
@@ -20178,7 +20178,7 @@
         <v>1.0822000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="76">
         <v>42125</v>
       </c>
@@ -20186,7 +20186,7 @@
         <v>1.1167</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="76">
         <v>42156</v>
       </c>
@@ -20194,7 +20194,7 @@
         <v>1.1226</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="76">
         <v>42186</v>
       </c>
@@ -20202,7 +20202,7 @@
         <v>1.0996999999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="76">
         <v>42217</v>
       </c>
@@ -20210,7 +20210,7 @@
         <v>1.1135999999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="76">
         <v>42248</v>
       </c>
@@ -20218,7 +20218,7 @@
         <v>1.1229</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="76">
         <v>42278</v>
       </c>
@@ -20226,7 +20226,7 @@
         <v>1.1228</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="76">
         <v>42309</v>
       </c>
@@ -20234,7 +20234,7 @@
         <v>1.0727</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="76">
         <v>42339</v>
       </c>
@@ -20242,7 +20242,7 @@
         <v>1.0889</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="76">
         <v>42370</v>
       </c>
@@ -20250,7 +20250,7 @@
         <v>1.0854999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="76">
         <v>42401</v>
       </c>
@@ -20258,7 +20258,7 @@
         <v>1.1092</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="76">
         <v>42430</v>
       </c>
@@ -20266,7 +20266,7 @@
         <v>1.1133999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="76">
         <v>42461</v>
       </c>
@@ -20274,7 +20274,7 @@
         <v>1.1346000000000001</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="76">
         <v>42491</v>
       </c>
@@ -20282,7 +20282,7 @@
         <v>1.1312</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="76">
         <v>42522</v>
       </c>
@@ -20290,7 +20290,7 @@
         <v>1.1232</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="76">
         <v>42552</v>
       </c>
@@ -20298,7 +20298,7 @@
         <v>1.1054999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="76">
         <v>42583</v>
       </c>
@@ -20306,7 +20306,7 @@
         <v>1.1207</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="76">
         <v>42614</v>
       </c>
@@ -20314,7 +20314,7 @@
         <v>1.1217999999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="76">
         <v>42644</v>
       </c>
@@ -20322,7 +20322,7 @@
         <v>1.1013999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="76">
         <v>42675</v>
       </c>
@@ -20330,7 +20330,7 @@
         <v>1.0791999999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="76">
         <v>42705</v>
       </c>
@@ -20338,7 +20338,7 @@
         <v>1.0545</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="76">
         <v>42736</v>
       </c>
@@ -20346,7 +20346,7 @@
         <v>1.0634999999999999</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="76">
         <v>42767</v>
       </c>
@@ -20354,7 +20354,7 @@
         <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="76">
         <v>42795</v>
       </c>
@@ -20362,7 +20362,7 @@
         <v>1.0690999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="76">
         <v>42826</v>
       </c>
@@ -20370,7 +20370,7 @@
         <v>1.0713999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="76">
         <v>42856</v>
       </c>
@@ -20378,7 +20378,7 @@
         <v>1.105</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="76">
         <v>42887</v>
       </c>
@@ -20386,7 +20386,7 @@
         <v>1.1233</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="76">
         <v>42917</v>
       </c>
@@ -20394,7 +20394,7 @@
         <v>1.153</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="76">
         <v>42948</v>
       </c>
@@ -20402,7 +20402,7 @@
         <v>1.1813</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="76">
         <v>42979</v>
       </c>
@@ -20410,7 +20410,7 @@
         <v>1.1913</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="76">
         <v>43009</v>
       </c>
@@ -20418,7 +20418,7 @@
         <v>1.1755</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="76">
         <v>43040</v>
       </c>
@@ -20426,7 +20426,7 @@
         <v>1.1742999999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="76">
         <v>43070</v>
       </c>
@@ -20434,7 +20434,7 @@
         <v>1.1836</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="76">
         <v>43101</v>
       </c>
@@ -20442,7 +20442,7 @@
         <v>1.2197</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="76">
         <v>43132</v>
       </c>
@@ -20450,7 +20450,7 @@
         <v>1.234</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="76">
         <v>43160</v>
       </c>
@@ -20458,7 +20458,7 @@
         <v>1.2334000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="76">
         <v>43191</v>
       </c>
@@ -20466,7 +20466,7 @@
         <v>1.2270000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="76">
         <v>43221</v>
       </c>
@@ -20474,7 +20474,7 @@
         <v>1.1822999999999999</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="76">
         <v>43252</v>
       </c>
@@ -20482,7 +20482,7 @@
         <v>1.1678999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="76">
         <v>43282</v>
       </c>
@@ -20490,7 +20490,7 @@
         <v>1.1685000000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="76">
         <v>43313</v>
       </c>
@@ -20498,7 +20498,7 @@
         <v>1.1547000000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="76">
         <v>43344</v>
       </c>
@@ -20506,7 +20506,7 @@
         <v>1.1667000000000001</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="76">
         <v>43374</v>
       </c>
@@ -20514,7 +20514,7 @@
         <v>1.1488</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="76">
         <v>43405</v>
       </c>
@@ -20522,7 +20522,7 @@
         <v>1.1364000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="76">
         <v>43435</v>
       </c>
@@ -20530,7 +20530,7 @@
         <v>1.1379999999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="76">
         <v>43466</v>
       </c>
@@ -20538,7 +20538,7 @@
         <v>1.1417999999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="76">
         <v>43497</v>
       </c>
@@ -20546,7 +20546,7 @@
         <v>1.1349</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="76">
         <v>43525</v>
       </c>
@@ -20554,7 +20554,7 @@
         <v>1.1295999999999999</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="76">
         <v>43556</v>
       </c>
@@ -20562,7 +20562,7 @@
         <v>1.1234</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="76">
         <v>43586</v>
       </c>
@@ -20570,7 +20570,7 @@
         <v>1.1187</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="76">
         <v>43617</v>
       </c>
@@ -20578,7 +20578,7 @@
         <v>1.1294999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="76">
         <v>43647</v>
       </c>
@@ -20586,7 +20586,7 @@
         <v>1.1211</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="76">
         <v>43678</v>
       </c>
@@ -20594,7 +20594,7 @@
         <v>1.1129</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="76">
         <v>43709</v>
       </c>
@@ -20602,7 +20602,7 @@
         <v>1.1011</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="76">
         <v>43739</v>
       </c>
@@ -20610,7 +20610,7 @@
         <v>1.1057999999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="76">
         <v>43770</v>
       </c>
@@ -20618,7 +20618,7 @@
         <v>1.1051</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="76">
         <v>43800</v>
       </c>
@@ -20626,7 +20626,7 @@
         <v>1.1113999999999999</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="76">
         <v>43831</v>
       </c>
@@ -20634,7 +20634,7 @@
         <v>1.1097999999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="76">
         <v>43862</v>
       </c>
@@ -20642,7 +20642,7 @@
         <v>1.0911</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="76">
         <v>43891</v>
       </c>
@@ -20650,7 +20650,7 @@
         <v>1.1046</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="76">
         <v>43922</v>
       </c>
@@ -20658,7 +20658,7 @@
         <v>1.0871</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="76">
         <v>43952</v>
       </c>
@@ -20666,7 +20666,7 @@
         <v>1.0907</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="76">
         <v>43983</v>
       </c>
@@ -20674,7 +20674,7 @@
         <v>1.1258999999999999</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="76">
         <v>44013</v>
       </c>
@@ -20682,7 +20682,7 @@
         <v>1.1488</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="76">
         <v>44044</v>
       </c>
@@ -20690,7 +20690,7 @@
         <v>1.1831</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="76">
         <v>44075</v>
       </c>
@@ -20698,7 +20698,7 @@
         <v>1.1785000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="76">
         <v>44105</v>
       </c>
@@ -20706,7 +20706,7 @@
         <v>1.1768000000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="76">
         <v>44136</v>
       </c>
@@ -20714,7 +20714,7 @@
         <v>1.1826000000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="76">
         <v>44166</v>
       </c>
@@ -20722,7 +20722,7 @@
         <v>1.2168000000000001</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="76">
         <v>44197</v>
       </c>
@@ -20730,7 +20730,7 @@
         <v>1.2178</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="76">
         <v>44228</v>
       </c>
@@ -20738,7 +20738,7 @@
         <v>1.2094</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="76">
         <v>44256</v>
       </c>
@@ -20746,7 +20746,7 @@
         <v>1.1901999999999999</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="76">
         <v>44287</v>
       </c>
@@ -20754,7 +20754,7 @@
         <v>1.1964999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="76">
         <v>44317</v>
       </c>
@@ -20762,7 +20762,7 @@
         <v>1.2145999999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="76">
         <v>44348</v>
       </c>
@@ -20770,7 +20770,7 @@
         <v>1.2048000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="76">
         <v>44378</v>
       </c>
@@ -20778,7 +20778,7 @@
         <v>1.1820999999999999</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="76">
         <v>44409</v>
       </c>
@@ -20786,7 +20786,7 @@
         <v>1.1767000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="76">
         <v>44440</v>
       </c>
@@ -20794,7 +20794,7 @@
         <v>1.1765000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="76">
         <v>44470</v>
       </c>
@@ -20802,7 +20802,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="76">
         <v>44501</v>
       </c>
@@ -20810,7 +20810,7 @@
         <v>1.1415999999999999</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="76">
         <v>44531</v>
       </c>
@@ -20818,7 +20818,7 @@
         <v>1.1301000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="76">
         <v>44562</v>
       </c>
@@ -20826,7 +20826,7 @@
         <v>1.1316999999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="76">
         <v>44593</v>
       </c>
@@ -20834,7 +20834,7 @@
         <v>1.1349</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="76">
         <v>44621</v>
       </c>
@@ -20842,7 +20842,7 @@
         <v>1.1019000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="76">
         <v>44652</v>
       </c>
@@ -20850,7 +20850,7 @@
         <v>1.0803</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="76">
         <v>44682</v>
       </c>
@@ -20858,7 +20858,7 @@
         <v>1.0567</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="76">
         <v>44713</v>
       </c>
@@ -20866,7 +20866,7 @@
         <v>1.0567</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="76">
         <v>44743</v>
       </c>
@@ -20874,7 +20874,7 @@
         <v>1.0167999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="76">
         <v>44774</v>
       </c>
@@ -20882,7 +20882,7 @@
         <v>1.0128999999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="76">
         <v>44805</v>
       </c>
@@ -20890,7 +20890,7 @@
         <v>0.9899</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="76">
         <v>44835</v>
       </c>
@@ -20898,7 +20898,7 @@
         <v>0.98529999999999995</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="76">
         <v>44866</v>
       </c>
@@ -20906,7 +20906,7 @@
         <v>1.0192000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="76">
         <v>44896</v>
       </c>
@@ -20914,7 +20914,7 @@
         <v>1.0590999999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="76">
         <v>44927</v>
       </c>
@@ -20922,7 +20922,7 @@
         <v>1.0777000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="76">
         <v>44958</v>
       </c>
@@ -20930,7 +20930,7 @@
         <v>1.0702</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="76">
         <v>44986</v>
       </c>
@@ -20938,7 +20938,7 @@
         <v>1.0710999999999999</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="76">
         <v>45017</v>
       </c>
@@ -20946,7 +20946,7 @@
         <v>1.0962000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="76">
         <v>45047</v>
       </c>
@@ -20954,7 +20954,7 @@
         <v>1.0867</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="76">
         <v>45078</v>
       </c>
@@ -20962,7 +20962,7 @@
         <v>1.0840000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="76">
         <v>45108</v>
       </c>
@@ -20970,7 +20970,7 @@
         <v>1.1067</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="76">
         <v>45139</v>
       </c>
@@ -20978,7 +20978,7 @@
         <v>1.091</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="76">
         <v>45170</v>
       </c>
@@ -20986,7 +20986,7 @@
         <v>1.0671999999999999</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="76">
         <v>45200</v>
       </c>
@@ -20994,7 +20994,7 @@
         <v>1.0565</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="76">
         <v>45231</v>
       </c>
@@ -21002,7 +21002,7 @@
         <v>1.0819000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="76">
         <v>45261</v>
       </c>
@@ -21010,7 +21010,7 @@
         <v>1.0909</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="76">
         <v>45292</v>
       </c>
@@ -21018,7 +21018,7 @@
         <v>1.0899000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="76">
         <v>45323</v>
       </c>
@@ -21026,7 +21026,7 @@
         <v>1.0792999999999999</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="76">
         <v>45352</v>
       </c>
@@ -21034,7 +21034,7 @@
         <v>1.087</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="76">
         <v>45383</v>
       </c>
@@ -21042,7 +21042,7 @@
         <v>1.0724</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="76">
         <v>45413</v>
       </c>
@@ -21050,7 +21050,7 @@
         <v>1.081</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="76">
         <v>45444</v>
       </c>
@@ -21058,7 +21058,7 @@
         <v>1.0763</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="76">
         <v>45474</v>
       </c>
@@ -21066,7 +21066,7 @@
         <v>1.0847</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="76">
         <v>45505</v>
       </c>
@@ -21083,7 +21083,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06161075-588E-5843-BB7A-EDB11B09427F}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21095,15 +21095,15 @@
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -21117,7 +21117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -21131,12 +21131,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -21153,7 +21153,7 @@
         <v>2.453282945060923E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -21161,7 +21161,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -21170,12 +21170,12 @@
         <v>0.81870109796004231</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="57" t="s">
         <v>15</v>
       </c>
@@ -21193,7 +21193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="57" t="s">
         <v>15</v>
       </c>
@@ -21210,7 +21210,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="105" t="s">
         <v>19</v>
       </c>
@@ -21227,7 +21227,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="105" t="s">
         <v>19</v>
       </c>
@@ -21244,7 +21244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="105" t="s">
         <v>19</v>
       </c>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="E13" s="94"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="105" t="s">
         <v>19</v>
       </c>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="E14" s="94"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="105" t="s">
         <v>22</v>
       </c>
@@ -21293,7 +21293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="105" t="s">
         <v>22</v>
       </c>
@@ -21310,7 +21310,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="105" t="s">
         <v>22</v>
       </c>
@@ -21326,7 +21326,7 @@
       </c>
       <c r="E17" s="94"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="105" t="s">
         <v>22</v>
       </c>
@@ -21342,7 +21342,7 @@
       </c>
       <c r="E18" s="94"/>
     </row>
-    <row r="19" spans="1:5" s="94" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="94" t="s">
         <v>23</v>
       </c>
@@ -21356,7 +21356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="94" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="94" t="s">
         <v>25</v>
       </c>
@@ -21370,7 +21370,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="94" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="94" t="s">
         <v>26</v>
       </c>
@@ -21385,12 +21385,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -21407,7 +21407,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -21424,12 +21424,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="57" t="s">
         <v>32</v>
       </c>
@@ -21446,7 +21446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="57" t="s">
         <v>32</v>
       </c>
@@ -21463,7 +21463,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="108" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" s="108" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="108" t="s">
         <v>33</v>
       </c>
@@ -21491,17 +21491,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E1155D-2A55-0744-BB3C-78DAEE3CB015}">
   <dimension ref="A1:AN55"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.09765625" customWidth="1"/>
-    <col min="2" max="2" width="20.09765625" customWidth="1"/>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="20.125" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="35" max="35" width="8.59765625" style="47"/>
-    <col min="36" max="36" width="17.09765625" style="41" customWidth="1"/>
-    <col min="37" max="37" width="13.59765625" customWidth="1"/>
+    <col min="35" max="35" width="8.625" style="47"/>
+    <col min="36" max="36" width="17.125" style="41" customWidth="1"/>
+    <col min="37" max="37" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
         <v>35</v>
       </c>
@@ -21617,7 +21617,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>43</v>
       </c>
@@ -21734,7 +21734,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="40" t="s">
         <v>51</v>
       </c>
@@ -21841,7 +21841,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
         <v>53</v>
       </c>
@@ -21948,7 +21948,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
         <v>55</v>
       </c>
@@ -22055,7 +22055,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="40" t="s">
         <v>56</v>
       </c>
@@ -22162,7 +22162,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="40" t="s">
         <v>57</v>
       </c>
@@ -22269,7 +22269,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="40" t="s">
         <v>58</v>
       </c>
@@ -22376,7 +22376,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="40" t="s">
         <v>59</v>
       </c>
@@ -22483,7 +22483,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
         <v>60</v>
       </c>
@@ -22590,7 +22590,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="40" t="s">
         <v>61</v>
       </c>
@@ -22697,7 +22697,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="40" t="s">
         <v>62</v>
       </c>
@@ -22804,7 +22804,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
         <v>63</v>
       </c>
@@ -22911,7 +22911,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
         <v>43</v>
       </c>
@@ -23028,7 +23028,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" s="40" t="s">
         <v>64</v>
       </c>
@@ -23135,7 +23135,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
         <v>65</v>
       </c>
@@ -23242,7 +23242,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" s="40" t="s">
         <v>66</v>
       </c>
@@ -23349,7 +23349,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" s="40" t="s">
         <v>67</v>
       </c>
@@ -23456,7 +23456,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" s="40" t="s">
         <v>68</v>
       </c>
@@ -23573,7 +23573,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" s="40" t="s">
         <v>51</v>
       </c>
@@ -23680,7 +23680,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
         <v>53</v>
       </c>
@@ -23787,7 +23787,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>55</v>
       </c>
@@ -23894,7 +23894,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" s="40" t="s">
         <v>56</v>
       </c>
@@ -24001,7 +24001,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
         <v>57</v>
       </c>
@@ -24108,7 +24108,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" s="40" t="s">
         <v>58</v>
       </c>
@@ -24215,7 +24215,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" s="40" t="s">
         <v>59</v>
       </c>
@@ -24322,7 +24322,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" s="40" t="s">
         <v>60</v>
       </c>
@@ -24429,7 +24429,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" s="40" t="s">
         <v>61</v>
       </c>
@@ -24536,7 +24536,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" s="40" t="s">
         <v>62</v>
       </c>
@@ -24643,7 +24643,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" s="40" t="s">
         <v>63</v>
       </c>
@@ -24750,7 +24750,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:38" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:38" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="34" t="s">
         <v>43</v>
       </c>
@@ -24867,7 +24867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" s="40" t="s">
         <v>64</v>
       </c>
@@ -24974,7 +24974,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
         <v>65</v>
       </c>
@@ -25081,7 +25081,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="40" t="s">
         <v>66</v>
       </c>
@@ -25188,7 +25188,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="40" t="s">
         <v>67</v>
       </c>
@@ -25295,7 +25295,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" s="40" t="s">
         <v>68</v>
       </c>
@@ -25412,7 +25412,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" s="40" t="s">
         <v>72</v>
       </c>
@@ -25439,7 +25439,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38" s="40" t="s">
         <v>72</v>
       </c>
@@ -25463,7 +25463,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39" s="40" t="s">
         <v>75</v>
       </c>
@@ -25496,7 +25496,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40" s="40" t="s">
         <v>75</v>
       </c>
@@ -25517,14 +25517,14 @@
         <v>1.89E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>79</v>
       </c>
       <c r="AI42"/>
       <c r="AJ42"/>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43" s="97"/>
       <c r="B43" s="98" t="s">
         <v>80</v>
@@ -25550,7 +25550,7 @@
       <c r="AI43"/>
       <c r="AJ43"/>
     </row>
-    <row r="44" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="99" t="s">
         <v>87</v>
       </c>
@@ -25579,7 +25579,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45" s="97"/>
       <c r="B45" s="100" t="s">
         <v>88</v>
@@ -25608,7 +25608,7 @@
       <c r="AI45"/>
       <c r="AJ45"/>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46" s="97"/>
       <c r="B46" s="100" t="s">
         <v>88</v>
@@ -25637,7 +25637,7 @@
       <c r="AI46"/>
       <c r="AJ46"/>
     </row>
-    <row r="47" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="99" t="s">
         <v>94</v>
       </c>
@@ -25668,44 +25668,44 @@
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>98</v>
       </c>
       <c r="AI48"/>
       <c r="AJ48"/>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>99</v>
       </c>
       <c r="AI49"/>
       <c r="AJ49"/>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>100</v>
       </c>
       <c r="AI50"/>
       <c r="AJ50"/>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AI51"/>
       <c r="AJ51"/>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AI52"/>
       <c r="AJ52"/>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AI53"/>
       <c r="AJ53"/>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AI54"/>
       <c r="AJ54"/>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AI55"/>
       <c r="AJ55"/>
     </row>
@@ -25727,17 +25727,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C700A40-351E-EE4C-92AD-3BC93D7F11F0}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AR27"/>
-  <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.59765625" style="10"/>
-    <col min="2" max="2" width="69.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="10"/>
+    <col min="2" max="2" width="69.625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="10.59765625" style="10"/>
+    <col min="6" max="16384" width="10.625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -25783,7 +25783,7 @@
       <c r="AQ1" s="9"/>
       <c r="AR1" s="9"/>
     </row>
-    <row r="2" spans="1:44" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:44" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9"/>
       <c r="B2" s="11" t="s">
         <v>101</v>
@@ -25831,7 +25831,7 @@
       <c r="AQ2" s="9"/>
       <c r="AR2" s="9"/>
     </row>
-    <row r="3" spans="1:44" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -25877,7 +25877,7 @@
       <c r="AQ3" s="9"/>
       <c r="AR3" s="9"/>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
         <v>102</v>
@@ -25927,7 +25927,7 @@
       <c r="AQ4" s="9"/>
       <c r="AR4" s="9"/>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="9" t="s">
         <v>6</v>
@@ -26035,7 +26035,7 @@
       <c r="AQ5" s="15"/>
       <c r="AR5" s="15"/>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" s="16" t="s">
         <v>105</v>
@@ -26141,7 +26141,7 @@
       <c r="AQ6" s="19"/>
       <c r="AR6" s="19"/>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A7" s="20"/>
       <c r="B7" s="20" t="s">
         <v>106</v>
@@ -26247,7 +26247,7 @@
       <c r="AQ7" s="24"/>
       <c r="AR7" s="24"/>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="25"/>
@@ -26293,7 +26293,7 @@
       <c r="AQ8" s="25"/>
       <c r="AR8" s="25"/>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="12" t="s">
         <v>107</v>
@@ -26341,7 +26341,7 @@
       <c r="AQ9" s="25"/>
       <c r="AR9" s="25"/>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="12" t="s">
         <v>108</v>
@@ -26389,7 +26389,7 @@
       <c r="AQ10" s="25"/>
       <c r="AR10" s="25"/>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="12" t="s">
         <v>109</v>
@@ -26495,7 +26495,7 @@
       <c r="AQ11" s="25"/>
       <c r="AR11" s="25"/>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="12" t="s">
         <v>110</v>
@@ -26543,7 +26543,7 @@
       <c r="AQ12" s="25"/>
       <c r="AR12" s="25"/>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="12" t="s">
         <v>109</v>
@@ -26649,7 +26649,7 @@
       <c r="AQ13" s="9"/>
       <c r="AR13" s="9"/>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="12" t="s">
         <v>111</v>
@@ -26697,7 +26697,7 @@
       <c r="AQ14" s="9"/>
       <c r="AR14" s="9"/>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="12" t="s">
         <v>109</v>
@@ -26803,7 +26803,7 @@
       <c r="AQ15" s="9"/>
       <c r="AR15" s="9"/>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="25"/>
@@ -26849,7 +26849,7 @@
       <c r="AQ16" s="9"/>
       <c r="AR16" s="9"/>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -26895,7 +26895,7 @@
       <c r="AQ17" s="9"/>
       <c r="AR17" s="9"/>
     </row>
-    <row r="18" spans="1:44" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:44" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
       <c r="B18" s="11" t="s">
         <v>112</v>
@@ -26943,7 +26943,7 @@
       <c r="AQ18" s="9"/>
       <c r="AR18" s="9"/>
     </row>
-    <row r="19" spans="1:44" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:44" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -26989,7 +26989,7 @@
       <c r="AQ19" s="9"/>
       <c r="AR19" s="9"/>
     </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -27036,7 +27036,7 @@
       <c r="AQ20" s="9"/>
       <c r="AR20" s="9"/>
     </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
       <c r="B21" s="9" t="s">
         <v>112</v>
@@ -27087,7 +27087,7 @@
       <c r="AQ21" s="9"/>
       <c r="AR21" s="9"/>
     </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -27133,7 +27133,7 @@
       <c r="AQ22" s="9"/>
       <c r="AR22" s="9"/>
     </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -27179,7 +27179,7 @@
       <c r="AQ23" s="9"/>
       <c r="AR23" s="9"/>
     </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
@@ -27221,7 +27221,7 @@
       <c r="AQ24" s="9"/>
       <c r="AR24" s="9"/>
     </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -27267,7 +27267,7 @@
       <c r="AQ25" s="9"/>
       <c r="AR25" s="9"/>
     </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -27313,7 +27313,7 @@
       <c r="AQ26" s="9"/>
       <c r="AR26" s="9"/>
     </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -27367,20 +27367,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6861D5-92D2-D641-8B69-D340B89E733B}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="144" t="s">
         <v>114</v>
       </c>
       <c r="B1" s="144"/>
       <c r="C1" s="144"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -27388,7 +27388,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>406</v>
       </c>
@@ -27396,7 +27396,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>358</v>
       </c>
@@ -27404,7 +27404,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>117</v>
       </c>
@@ -27416,13 +27416,13 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="144" t="s">
         <v>119</v>
       </c>
       <c r="B9" s="144"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>2024</v>
       </c>
@@ -27430,7 +27430,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>120</v>
       </c>
@@ -27444,7 +27444,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>121</v>
       </c>
@@ -27455,13 +27455,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="144" t="s">
         <v>122</v>
       </c>
       <c r="B14" s="144"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>2024</v>
       </c>
@@ -27469,7 +27469,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>120</v>
       </c>
@@ -27480,7 +27480,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -27508,13 +27508,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B5CED7-41F6-FF44-BBF4-DBE0D457C1E0}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A2:C2"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -27533,31 +27533,31 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA419E9D-493B-4DCE-A933-2A9A9AF40246}">
   <dimension ref="A1:AD57"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" outlineLevelCol="2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" outlineLevelCol="2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.09765625" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="8.8984375" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.125" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="8.875" hidden="1" customWidth="1" outlineLevel="2"/>
     <col min="4" max="4" width="7" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="5" max="5" width="11.59765625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="6" max="6" width="16.59765625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="7" max="8" width="8.8984375" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="9" max="9" width="10.59765625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="10" max="10" width="8.3984375" bestFit="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="5" max="5" width="11.625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="6" max="6" width="16.625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="7" max="8" width="8.875" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="9" max="9" width="10.625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="10" max="10" width="8.375" bestFit="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="12" max="13" width="8" customWidth="1"/>
-    <col min="14" max="15" width="16.59765625" customWidth="1"/>
-    <col min="16" max="16" width="20.59765625" customWidth="1"/>
+    <col min="14" max="15" width="16.625" customWidth="1"/>
+    <col min="16" max="16" width="20.625" customWidth="1"/>
     <col min="17" max="17" width="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.09765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="37.69921875" customWidth="1"/>
-    <col min="20" max="20" width="34.19921875" customWidth="1"/>
-    <col min="21" max="21" width="33.8984375" customWidth="1"/>
-    <col min="22" max="22" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="24" max="30" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="37.75" customWidth="1"/>
+    <col min="20" max="20" width="34.25" customWidth="1"/>
+    <col min="21" max="21" width="33.875" customWidth="1"/>
+    <col min="22" max="22" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="30" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
@@ -27641,7 +27641,7 @@
       <c r="AC1" s="82"/>
       <c r="AD1" s="82"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -27697,7 +27697,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>150</v>
       </c>
@@ -27753,7 +27753,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>150</v>
       </c>
@@ -27807,7 +27807,7 @@
       </c>
       <c r="W4" s="60"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>150</v>
       </c>
@@ -27861,7 +27861,7 @@
       </c>
       <c r="W5" s="60"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>150</v>
       </c>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="W6" s="60"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>150</v>
       </c>
@@ -27969,7 +27969,7 @@
       </c>
       <c r="W7" s="60"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>150</v>
       </c>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="W8" s="60"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="W9" s="60"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -28131,7 +28131,7 @@
       </c>
       <c r="W10" s="60"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -28185,7 +28185,7 @@
       </c>
       <c r="W11" s="60"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>150</v>
       </c>
@@ -28239,7 +28239,7 @@
       </c>
       <c r="W12" s="60"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>150</v>
       </c>
@@ -28293,7 +28293,7 @@
       </c>
       <c r="W13" s="60"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>150</v>
       </c>
@@ -28347,7 +28347,7 @@
       </c>
       <c r="W14" s="60"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>150</v>
       </c>
@@ -28401,7 +28401,7 @@
       </c>
       <c r="W15" s="60"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>150</v>
       </c>
@@ -28458,7 +28458,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>150</v>
       </c>
@@ -28515,7 +28515,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>150</v>
       </c>
@@ -28557,7 +28557,7 @@
       </c>
       <c r="W18" s="60"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>150</v>
       </c>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="W19" s="60"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>150</v>
       </c>
@@ -28635,7 +28635,7 @@
       </c>
       <c r="W20" s="60"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>150</v>
       </c>
@@ -28671,7 +28671,7 @@
       </c>
       <c r="W21" s="60"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>150</v>
       </c>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="W22" s="60"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>150</v>
       </c>
@@ -28743,7 +28743,7 @@
       </c>
       <c r="W23" s="60"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -28785,7 +28785,7 @@
       </c>
       <c r="W24" s="60"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>150</v>
       </c>
@@ -28836,7 +28836,7 @@
       </c>
       <c r="W25" s="60"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>150</v>
       </c>
@@ -28872,7 +28872,7 @@
       </c>
       <c r="W26" s="60"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>150</v>
       </c>
@@ -28908,7 +28908,7 @@
       </c>
       <c r="W27" s="60"/>
     </row>
-    <row r="28" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="48" t="s">
         <v>150</v>
       </c>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="W28" s="90"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>150</v>
       </c>
@@ -28974,7 +28974,7 @@
       </c>
       <c r="W29" s="60"/>
     </row>
-    <row r="30" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="48" t="s">
         <v>260</v>
       </c>
@@ -29007,7 +29007,7 @@
       </c>
       <c r="W30" s="90"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>150</v>
       </c>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="W31" s="60"/>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>150</v>
       </c>
@@ -29079,7 +29079,7 @@
       </c>
       <c r="W32" s="60"/>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>150</v>
       </c>
@@ -29115,7 +29115,7 @@
       </c>
       <c r="W33" s="60"/>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>150</v>
       </c>
@@ -29151,7 +29151,7 @@
       </c>
       <c r="W34" s="60"/>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>150</v>
       </c>
@@ -29202,7 +29202,7 @@
       </c>
       <c r="W35" s="60"/>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>150</v>
       </c>
@@ -29238,7 +29238,7 @@
       </c>
       <c r="W36" s="60"/>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>150</v>
       </c>
@@ -29274,7 +29274,7 @@
       </c>
       <c r="W37" s="60"/>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>150</v>
       </c>
@@ -29310,7 +29310,7 @@
       </c>
       <c r="W38" s="60"/>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>150</v>
       </c>
@@ -29346,7 +29346,7 @@
       </c>
       <c r="W39" s="60"/>
     </row>
-    <row r="40" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="48" t="s">
         <v>150</v>
       </c>
@@ -29373,7 +29373,7 @@
       </c>
       <c r="W40" s="90"/>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>150</v>
       </c>
@@ -29412,7 +29412,7 @@
       </c>
       <c r="W41" s="60"/>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>150</v>
       </c>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="W42" s="60"/>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -29487,7 +29487,7 @@
       </c>
       <c r="W43" s="60"/>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>150</v>
       </c>
@@ -29520,7 +29520,7 @@
       </c>
       <c r="W44" s="60"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>150</v>
       </c>
@@ -29553,7 +29553,7 @@
       </c>
       <c r="W45" s="60"/>
     </row>
-    <row r="46" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="48" t="s">
         <v>150</v>
       </c>
@@ -29580,7 +29580,7 @@
       </c>
       <c r="W46" s="90"/>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>260</v>
       </c>
@@ -29614,7 +29614,7 @@
       </c>
       <c r="W47" s="60"/>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>260</v>
       </c>
@@ -29648,7 +29648,7 @@
       </c>
       <c r="W48" s="60"/>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -29696,7 +29696,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>150</v>
       </c>
@@ -29744,7 +29744,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>150</v>
       </c>
@@ -29792,7 +29792,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>150</v>
       </c>
@@ -29840,7 +29840,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>150</v>
       </c>
@@ -29882,7 +29882,7 @@
       </c>
       <c r="W53" s="60"/>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>150</v>
       </c>
@@ -29918,7 +29918,7 @@
       </c>
       <c r="W54" s="60"/>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>150</v>
       </c>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="W55" s="60"/>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>150</v>
       </c>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="W56" s="60"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>150</v>
       </c>
@@ -30047,34 +30047,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99968075-C79E-496E-8470-A0201C505FA7}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AL54"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.09765625" customWidth="1"/>
-    <col min="2" max="2" width="9.09765625" customWidth="1"/>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="9.125" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="18.5" customWidth="1"/>
-    <col min="7" max="7" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.8984375" customWidth="1"/>
-    <col min="12" max="12" width="26.69921875" customWidth="1"/>
+    <col min="11" max="11" width="30.875" customWidth="1"/>
+    <col min="12" max="12" width="26.75" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="18.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.09765625" customWidth="1"/>
-    <col min="19" max="22" width="20.09765625" customWidth="1"/>
+    <col min="18" max="18" width="18.125" customWidth="1"/>
+    <col min="19" max="22" width="20.125" customWidth="1"/>
     <col min="24" max="25" width="17.5" customWidth="1"/>
-    <col min="26" max="28" width="15.09765625" customWidth="1"/>
+    <col min="26" max="28" width="15.125" customWidth="1"/>
     <col min="29" max="29" width="22.5" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="22.5" customWidth="1"/>
-    <col min="32" max="32" width="37.59765625" customWidth="1"/>
+    <col min="32" max="32" width="37.625" customWidth="1"/>
     <col min="33" max="33" width="19" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="19" customWidth="1"/>
-    <col min="36" max="36" width="33.59765625" customWidth="1"/>
+    <col min="36" max="36" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -30134,7 +30134,7 @@
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="117" t="s">
         <v>151</v>
       </c>
@@ -30165,7 +30165,7 @@
       <c r="R2" s="118"/>
       <c r="AI2" s="119"/>
     </row>
-    <row r="3" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="117" t="s">
         <v>151</v>
       </c>
@@ -30197,7 +30197,7 @@
       <c r="R3" s="118"/>
       <c r="AI3" s="119"/>
     </row>
-    <row r="4" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="117" t="s">
         <v>151</v>
       </c>
@@ -30229,7 +30229,7 @@
       <c r="R4" s="118"/>
       <c r="AI4" s="119"/>
     </row>
-    <row r="5" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="117" t="s">
         <v>151</v>
       </c>
@@ -30262,7 +30262,7 @@
       <c r="AD5" s="120"/>
       <c r="AI5" s="119"/>
     </row>
-    <row r="6" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="117" t="s">
         <v>185</v>
       </c>
@@ -30293,7 +30293,7 @@
       </c>
       <c r="R6" s="121"/>
     </row>
-    <row r="7" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="117" t="s">
         <v>185</v>
       </c>
@@ -30325,7 +30325,7 @@
       <c r="O7" s="122"/>
       <c r="R7" s="121"/>
     </row>
-    <row r="8" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="117" t="s">
         <v>185</v>
       </c>
@@ -30357,7 +30357,7 @@
       <c r="R8" s="121"/>
       <c r="AD8" s="120"/>
     </row>
-    <row r="9" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>199</v>
       </c>
@@ -30392,7 +30392,7 @@
       <c r="W9" s="114"/>
       <c r="AF9" s="115"/>
     </row>
-    <row r="10" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>208</v>
       </c>
@@ -30429,7 +30429,7 @@
       <c r="R10" s="113"/>
       <c r="AI10" s="116"/>
     </row>
-    <row r="11" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="117" t="s">
         <v>214</v>
       </c>
@@ -30460,7 +30460,7 @@
       <c r="R11" s="121"/>
       <c r="AI11" s="119"/>
     </row>
-    <row r="12" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="117" t="s">
         <v>214</v>
       </c>
@@ -30491,7 +30491,7 @@
       <c r="R12" s="121"/>
       <c r="AI12" s="119"/>
     </row>
-    <row r="13" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>223</v>
       </c>
@@ -30526,7 +30526,7 @@
       <c r="AA13" s="124"/>
       <c r="AB13" s="124"/>
     </row>
-    <row r="14" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>227</v>
       </c>
@@ -30563,7 +30563,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="15" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>230</v>
       </c>
@@ -30595,7 +30595,7 @@
       <c r="AI15" s="116"/>
       <c r="AL15" s="127"/>
     </row>
-    <row r="16" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>230</v>
       </c>
@@ -30627,7 +30627,7 @@
       <c r="AI16" s="116"/>
       <c r="AL16" s="127"/>
     </row>
-    <row r="17" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>234</v>
       </c>
@@ -30658,7 +30658,7 @@
       <c r="R17" s="123"/>
       <c r="AI17" s="116"/>
     </row>
-    <row r="18" spans="1:36" s="128" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" s="128" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="128" t="s">
         <v>240</v>
       </c>
@@ -30686,7 +30686,7 @@
       <c r="R18" s="129"/>
       <c r="W18" s="130"/>
     </row>
-    <row r="19" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>247</v>
       </c>
@@ -30721,7 +30721,7 @@
       <c r="R19" s="123"/>
       <c r="X19" s="123"/>
     </row>
-    <row r="20" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>247</v>
       </c>
@@ -30753,7 +30753,7 @@
       <c r="R20" s="123"/>
       <c r="X20" s="123"/>
     </row>
-    <row r="21" spans="1:36" s="127" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" s="127" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="127" t="s">
         <v>251</v>
       </c>
@@ -30772,7 +30772,7 @@
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
     </row>
-    <row r="22" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>255</v>
       </c>
@@ -30814,7 +30814,7 @@
       <c r="AB22" s="124"/>
       <c r="AF22" s="115"/>
     </row>
-    <row r="23" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>267</v>
       </c>
@@ -30848,7 +30848,7 @@
       <c r="X23" s="123"/>
       <c r="AI23" s="116"/>
     </row>
-    <row r="24" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>267</v>
       </c>
@@ -30882,7 +30882,7 @@
       <c r="X24" s="123"/>
       <c r="AI24" s="116"/>
     </row>
-    <row r="25" spans="1:36" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60" t="s">
         <v>271</v>
       </c>
@@ -30906,7 +30906,7 @@
       </c>
       <c r="AI25" s="93"/>
     </row>
-    <row r="26" spans="1:36" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="117" t="s">
         <v>275</v>
       </c>
@@ -30936,7 +30936,7 @@
       </c>
       <c r="X26" s="138"/>
     </row>
-    <row r="27" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>278</v>
       </c>
@@ -30970,7 +30970,7 @@
       <c r="R27" s="126"/>
       <c r="X27" s="123"/>
     </row>
-    <row r="28" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="88" t="s">
         <v>285</v>
       </c>
@@ -30998,7 +30998,7 @@
       <c r="AI28" s="53"/>
       <c r="AJ28" s="48"/>
     </row>
-    <row r="29" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="88" t="s">
         <v>285</v>
       </c>
@@ -31026,7 +31026,7 @@
       <c r="AI29" s="53"/>
       <c r="AJ29" s="48"/>
     </row>
-    <row r="30" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="88" t="s">
         <v>285</v>
       </c>
@@ -31054,7 +31054,7 @@
       <c r="AI30" s="53"/>
       <c r="AJ30" s="48"/>
     </row>
-    <row r="31" spans="1:36" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" ht="25.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="88" t="s">
         <v>285</v>
       </c>
@@ -31083,7 +31083,7 @@
       <c r="AI31" s="53"/>
       <c r="AJ31" s="48"/>
     </row>
-    <row r="32" spans="1:36" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="48" t="s">
         <v>290</v>
       </c>
@@ -31100,7 +31100,7 @@
       <c r="AH32"/>
       <c r="AI32" s="87"/>
     </row>
-    <row r="33" spans="1:35" s="112" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:35" s="112" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="112" t="s">
         <v>294</v>
       </c>
@@ -31134,7 +31134,7 @@
       <c r="L33" s="41"/>
       <c r="X33" s="132"/>
     </row>
-    <row r="34" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>301</v>
       </c>
@@ -31165,7 +31165,7 @@
       <c r="Q34" s="127"/>
       <c r="AI34" s="116"/>
     </row>
-    <row r="35" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>307</v>
       </c>
@@ -31194,7 +31194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>311</v>
       </c>
@@ -31226,7 +31226,7 @@
       <c r="X36" s="133"/>
       <c r="AA36" s="134"/>
     </row>
-    <row r="37" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>315</v>
       </c>
@@ -31253,7 +31253,7 @@
       </c>
       <c r="R37" s="126"/>
     </row>
-    <row r="38" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="127" t="s">
         <v>319</v>
       </c>
@@ -31269,7 +31269,7 @@
       </c>
       <c r="F38" s="127"/>
     </row>
-    <row r="39" spans="1:35" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:35" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="122" t="s">
         <v>329</v>
       </c>
@@ -31301,7 +31301,7 @@
       <c r="R39" s="141"/>
       <c r="X39" s="141"/>
     </row>
-    <row r="40" spans="1:35" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:35" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="122" t="s">
         <v>329</v>
       </c>
@@ -31335,7 +31335,7 @@
       <c r="AE40" s="120"/>
       <c r="AF40" s="142"/>
     </row>
-    <row r="41" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="124" t="s">
         <v>336</v>
       </c>
@@ -31367,7 +31367,7 @@
       <c r="AD41" s="135"/>
       <c r="AE41" s="43"/>
     </row>
-    <row r="42" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="124" t="s">
         <v>342</v>
       </c>
@@ -31398,7 +31398,7 @@
       <c r="X42" s="123"/>
       <c r="AE42" s="43"/>
     </row>
-    <row r="43" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="124" t="s">
         <v>345</v>
       </c>
@@ -31446,7 +31446,7 @@
       <c r="AG43" s="2"/>
       <c r="AH43" s="2"/>
     </row>
-    <row r="44" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="124" t="s">
         <v>345</v>
       </c>
@@ -31494,7 +31494,7 @@
       <c r="AG44" s="2"/>
       <c r="AH44" s="2"/>
     </row>
-    <row r="45" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>348</v>
       </c>
@@ -31522,10 +31522,10 @@
       <c r="R45" s="123"/>
       <c r="X45" s="123"/>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" s="48"/>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="143" t="s">
         <v>35</v>
       </c>
@@ -31560,7 +31560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="143" t="s">
         <v>402</v>
       </c>
@@ -31579,7 +31579,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="143"/>
       <c r="C52" s="143" t="s">
         <v>404</v>
@@ -31596,7 +31596,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" s="143" t="s">
         <v>405</v>
       </c>
@@ -31615,7 +31615,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" s="143"/>
       <c r="C54" s="143" t="s">
         <v>404</v>

--- a/data/Master Standardisation DACCS_LE.xlsx
+++ b/data/Master Standardisation DACCS_LE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/ydubey_ethz_ch/Documents/Documents/GitHub/DACCSvDACCU/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6797" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B405949-A78B-4C0D-BDCA-D62C47D81B89}"/>
+  <xr:revisionPtr revIDLastSave="6799" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{282891B3-2452-4796-BEA8-5F60858E093D}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" tabRatio="973" firstSheet="6" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
+    <workbookView xWindow="39210" yWindow="630" windowWidth="28800" windowHeight="15345" tabRatio="973" firstSheet="6" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -11322,7 +11322,7 @@
   <sheetPr codeName="Sheet7" filterMode="1">
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:W180"/>
+  <dimension ref="A1:W181"/>
   <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.125" bestFit="1" customWidth="1"/>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="L176" s="30"/>
     </row>
-    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="L177" s="30"/>
     </row>
-    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="L178" s="30"/>
     </row>
-    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="str">
         <f>'Study Parameters'!A45</f>
         <v>APS 2011</v>
@@ -18994,7 +18994,7 @@
       </c>
       <c r="M179" s="30"/>
     </row>
-    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>348</v>
       </c>
@@ -19033,6 +19033,9 @@
         <v>1103.1106106220375</v>
       </c>
       <c r="M180" s="30"/>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O181" s="30"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:W180" xr:uid="{2D1B99AC-5C89-CE47-B699-CCA57CE6E758}">

--- a/data/Master Standardisation DACCS_LE.xlsx
+++ b/data/Master Standardisation DACCS_LE.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="6799" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{282891B3-2452-4796-BEA8-5F60858E093D}"/>
   <bookViews>
-    <workbookView xWindow="39210" yWindow="630" windowWidth="28800" windowHeight="15345" tabRatio="973" firstSheet="6" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
+    <workbookView xWindow="5790" yWindow="3765" windowWidth="28800" windowHeight="15345" tabRatio="973" firstSheet="6" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
